--- a/datos_y_modelos/Domestic/supra.xlsx
+++ b/datos_y_modelos/Domestic/supra.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bloomberglp-my.sharepoint.com/personal/tsiqueira4_bloomberg_com/Documents/Desktop/master_thesis_economics/datos_y_modelos/Domestic/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bloomberglp-my.sharepoint.com/personal/tsiqueira4_bloomberg_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{AD650BC0-82BC-4D6F-9B61-BA98BD7A85B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22DEFD1A-A79A-45EC-AA98-539743677AC1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{98CE6E99-448D-4B37-B3BD-6030979350D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EC0627F6-2DC6-4AF1-9A23-F0938631E874}"/>
+    <workbookView xWindow="-70" yWindow="10690" windowWidth="19420" windowHeight="11620" xr2:uid="{EC0627F6-2DC6-4AF1-9A23-F0938631E874}"/>
   </bookViews>
   <sheets>
     <sheet name="db_values_only" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,6 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
-    <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">db_values_only!$B$1:$AK$70</definedName>
@@ -88,7 +87,7 @@
     <definedName name="StartDate">'[1]General Information'!$C$8</definedName>
     <definedName name="STMonth">'[1]General Information'!$D$22</definedName>
     <definedName name="STYear">'[1]General Information'!$C$22</definedName>
-    <definedName name="ticker">'[3]Price Recommendations'!$C$7</definedName>
+    <definedName name="ticker">'[2]Price Recommendations'!$C$7</definedName>
     <definedName name="TICKERS">#REF!</definedName>
     <definedName name="X_Show_CapexDepr">[1]Sensitivity!$M$9</definedName>
     <definedName name="X_Show_DDE">[1]Sensitivity!$M$21</definedName>
@@ -123,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2016" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2027" uniqueCount="469">
   <si>
     <t>id</t>
   </si>
@@ -1515,13 +1514,39 @@
   </si>
   <si>
     <t>11/25/2022</t>
+  </si>
+  <si>
+    <t>dias para vencer</t>
+  </si>
+  <si>
+    <t>anos para vencer</t>
+  </si>
+  <si>
+    <t>PX_LAST</t>
+  </si>
+  <si>
+    <t>Face Value</t>
+  </si>
+  <si>
+    <t>Hoje</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1553,10 +1578,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1564,8 +1590,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3289,24 +3319,6 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="db_formulae"/>
-      <sheetName val="db_values_only"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3649,7 +3661,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E3BFF2A-B712-459A-8265-CC1EA8C41DE6}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="B1:AK70"/>
+  <dimension ref="B1:AQ70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -3679,9 +3691,13 @@
     <col min="35" max="35" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="9.140625" style="3"/>
+    <col min="40" max="40" width="12" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:37" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:43" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -3790,8 +3806,23 @@
       <c r="AK1" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="AL1" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="AM1" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>466</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>467</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>468</v>
+      </c>
     </row>
-    <row r="2" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>36</v>
       </c>
@@ -3900,8 +3931,30 @@
       <c r="AK2" t="s">
         <v>60</v>
       </c>
+      <c r="AL2" s="5">
+        <f ca="1">G2-$AQ$2</f>
+        <v>207</v>
+      </c>
+      <c r="AM2" s="3">
+        <f ca="1">AL2/365</f>
+        <v>0.56712328767123288</v>
+      </c>
+      <c r="AN2" t="str">
+        <f ca="1">IF(AM2&gt;36,"&gt;36y",ROUND(AM2,0)&amp;"y")</f>
+        <v>1y</v>
+      </c>
+      <c r="AO2">
+        <v>95.447999999999993</v>
+      </c>
+      <c r="AP2">
+        <v>1000</v>
+      </c>
+      <c r="AQ2" s="4">
+        <f ca="1">TODAY()</f>
+        <v>45837</v>
+      </c>
     </row>
-    <row r="3" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>61</v>
       </c>
@@ -4010,8 +4063,26 @@
       <c r="AK3" t="s">
         <v>60</v>
       </c>
+      <c r="AL3" s="5">
+        <f t="shared" ref="AL3:AL66" ca="1" si="0">G3-$AQ$2</f>
+        <v>961</v>
+      </c>
+      <c r="AM3" s="3">
+        <f t="shared" ref="AM3:AM66" ca="1" si="1">AL3/365</f>
+        <v>2.6328767123287671</v>
+      </c>
+      <c r="AN3" t="str">
+        <f t="shared" ref="AN3:AN66" ca="1" si="2">IF(AM3&gt;36,"&gt;36y",ROUND(AM3,0)&amp;"y")</f>
+        <v>3y</v>
+      </c>
+      <c r="AO3">
+        <v>96.543999999999997</v>
+      </c>
+      <c r="AP3">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="4" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>68</v>
       </c>
@@ -4120,8 +4191,26 @@
       <c r="AK4" t="s">
         <v>60</v>
       </c>
+      <c r="AL4" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>1321</v>
+      </c>
+      <c r="AM4" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>3.6191780821917807</v>
+      </c>
+      <c r="AN4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>4y</v>
+      </c>
+      <c r="AO4">
+        <v>92.878</v>
+      </c>
+      <c r="AP4">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="5" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>74</v>
       </c>
@@ -4230,8 +4319,26 @@
       <c r="AK5" t="s">
         <v>60</v>
       </c>
+      <c r="AL5" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>4607</v>
+      </c>
+      <c r="AM5" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>12.621917808219179</v>
+      </c>
+      <c r="AN5" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>13y</v>
+      </c>
+      <c r="AO5">
+        <v>25.390999999999998</v>
+      </c>
+      <c r="AP5">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="6" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>80</v>
       </c>
@@ -4340,8 +4447,26 @@
       <c r="AK6" t="s">
         <v>89</v>
       </c>
+      <c r="AL6" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>2409</v>
+      </c>
+      <c r="AM6" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>6.6</v>
+      </c>
+      <c r="AN6" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>7y</v>
+      </c>
+      <c r="AO6">
+        <v>47.192999999999998</v>
+      </c>
+      <c r="AP6">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="7" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>90</v>
       </c>
@@ -4450,8 +4575,26 @@
       <c r="AK7" t="s">
         <v>99</v>
       </c>
+      <c r="AL7" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>578</v>
+      </c>
+      <c r="AM7" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.5835616438356164</v>
+      </c>
+      <c r="AN7" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2y</v>
+      </c>
+      <c r="AO7">
+        <v>95.191000000000003</v>
+      </c>
+      <c r="AP7">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="8" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>100</v>
       </c>
@@ -4560,8 +4703,26 @@
       <c r="AK8" t="s">
         <v>60</v>
       </c>
+      <c r="AL8" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>2293</v>
+      </c>
+      <c r="AM8" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>6.2821917808219174</v>
+      </c>
+      <c r="AN8" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>6y</v>
+      </c>
+      <c r="AO8">
+        <v>94.566000000000003</v>
+      </c>
+      <c r="AP8">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="9" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>106</v>
       </c>
@@ -4670,8 +4831,26 @@
       <c r="AK9" t="s">
         <v>60</v>
       </c>
+      <c r="AL9" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>5720</v>
+      </c>
+      <c r="AM9" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>15.671232876712329</v>
+      </c>
+      <c r="AN9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>16y</v>
+      </c>
+      <c r="AO9">
+        <v>17.986000000000001</v>
+      </c>
+      <c r="AP9">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="10" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>111</v>
       </c>
@@ -4780,8 +4959,26 @@
       <c r="AK10" t="s">
         <v>121</v>
       </c>
+      <c r="AL10" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>221</v>
+      </c>
+      <c r="AM10" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.60547945205479448</v>
+      </c>
+      <c r="AN10" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>1y</v>
+      </c>
+      <c r="AO10">
+        <v>95.512</v>
+      </c>
+      <c r="AP10">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="11" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>122</v>
       </c>
@@ -4890,8 +5087,26 @@
       <c r="AK11" t="s">
         <v>99</v>
       </c>
+      <c r="AL11" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>458</v>
+      </c>
+      <c r="AM11" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.2547945205479452</v>
+      </c>
+      <c r="AN11" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>1y</v>
+      </c>
+      <c r="AO11">
+        <v>94.183999999999997</v>
+      </c>
+      <c r="AP11">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="12" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>128</v>
       </c>
@@ -5000,8 +5215,26 @@
       <c r="AK12" t="s">
         <v>99</v>
       </c>
+      <c r="AL12" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>122</v>
+      </c>
+      <c r="AM12" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.33424657534246577</v>
+      </c>
+      <c r="AN12" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>0y</v>
+      </c>
+      <c r="AO12">
+        <v>97.18</v>
+      </c>
+      <c r="AP12">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="13" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>134</v>
       </c>
@@ -5110,8 +5343,26 @@
       <c r="AK13" t="s">
         <v>143</v>
       </c>
+      <c r="AL13" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>6084</v>
+      </c>
+      <c r="AM13" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>16.668493150684931</v>
+      </c>
+      <c r="AN13" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>17y</v>
+      </c>
+      <c r="AO13">
+        <v>16.827999999999999</v>
+      </c>
+      <c r="AP13">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="14" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>144</v>
       </c>
@@ -5220,8 +5471,26 @@
       <c r="AK14" t="s">
         <v>99</v>
       </c>
+      <c r="AL14" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>3523</v>
+      </c>
+      <c r="AM14" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>9.6520547945205486</v>
+      </c>
+      <c r="AN14" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>10y</v>
+      </c>
+      <c r="AO14">
+        <v>34.139000000000003</v>
+      </c>
+      <c r="AP14">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="15" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>149</v>
       </c>
@@ -5330,8 +5599,26 @@
       <c r="AK15" t="s">
         <v>60</v>
       </c>
+      <c r="AL15" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>929</v>
+      </c>
+      <c r="AM15" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.5452054794520547</v>
+      </c>
+      <c r="AN15" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>3y</v>
+      </c>
+      <c r="AO15">
+        <v>86.379000000000005</v>
+      </c>
+      <c r="AP15">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="16" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>155</v>
       </c>
@@ -5440,8 +5727,26 @@
       <c r="AK16" t="s">
         <v>60</v>
       </c>
+      <c r="AL16" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>4349</v>
+      </c>
+      <c r="AM16" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>11.915068493150685</v>
+      </c>
+      <c r="AN16" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>12y</v>
+      </c>
+      <c r="AO16">
+        <v>26.757999999999999</v>
+      </c>
+      <c r="AP16">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="17" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>160</v>
       </c>
@@ -5550,8 +5855,26 @@
       <c r="AK17" t="s">
         <v>89</v>
       </c>
+      <c r="AL17" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>1055</v>
+      </c>
+      <c r="AM17" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.8904109589041096</v>
+      </c>
+      <c r="AN17" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>3y</v>
+      </c>
+      <c r="AO17">
+        <v>71.447000000000003</v>
+      </c>
+      <c r="AP17">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="18" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>165</v>
       </c>
@@ -5660,8 +5983,26 @@
       <c r="AK18" t="s">
         <v>60</v>
       </c>
+      <c r="AL18" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>1786</v>
+      </c>
+      <c r="AM18" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>4.8931506849315065</v>
+      </c>
+      <c r="AN18" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>5y</v>
+      </c>
+      <c r="AO18">
+        <v>57.503</v>
+      </c>
+      <c r="AP18">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="19" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>170</v>
       </c>
@@ -5770,8 +6111,26 @@
       <c r="AK19" t="s">
         <v>60</v>
       </c>
+      <c r="AL19" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>1662</v>
+      </c>
+      <c r="AM19" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>4.5534246575342463</v>
+      </c>
+      <c r="AN19" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>5y</v>
+      </c>
+      <c r="AO19">
+        <v>100.86799999999999</v>
+      </c>
+      <c r="AP19">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="20" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>176</v>
       </c>
@@ -5880,8 +6239,26 @@
       <c r="AK20" t="s">
         <v>121</v>
       </c>
+      <c r="AL20" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>2818</v>
+      </c>
+      <c r="AM20" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>7.720547945205479</v>
+      </c>
+      <c r="AN20" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>8y</v>
+      </c>
+      <c r="AO20">
+        <v>99.254999999999995</v>
+      </c>
+      <c r="AP20">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="21" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>182</v>
       </c>
@@ -5990,8 +6367,26 @@
       <c r="AK21" t="s">
         <v>60</v>
       </c>
+      <c r="AL21" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>1520</v>
+      </c>
+      <c r="AM21" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>4.1643835616438354</v>
+      </c>
+      <c r="AN21" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>4y</v>
+      </c>
+      <c r="AO21">
+        <v>101.663</v>
+      </c>
+      <c r="AP21">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="22" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>188</v>
       </c>
@@ -6100,8 +6495,26 @@
       <c r="AK22" t="s">
         <v>60</v>
       </c>
+      <c r="AL22" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>1571</v>
+      </c>
+      <c r="AM22" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>4.3041095890410963</v>
+      </c>
+      <c r="AN22" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>4y</v>
+      </c>
+      <c r="AO22">
+        <v>93.031999999999996</v>
+      </c>
+      <c r="AP22">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="23" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>194</v>
       </c>
@@ -6210,8 +6623,26 @@
       <c r="AK23" t="s">
         <v>60</v>
       </c>
+      <c r="AL23" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>4643</v>
+      </c>
+      <c r="AM23" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>12.72054794520548</v>
+      </c>
+      <c r="AN23" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>13y</v>
+      </c>
+      <c r="AO23">
+        <v>24.634</v>
+      </c>
+      <c r="AP23">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="24" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>199</v>
       </c>
@@ -6320,8 +6751,26 @@
       <c r="AK24" t="s">
         <v>60</v>
       </c>
+      <c r="AL24" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>271</v>
+      </c>
+      <c r="AM24" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.74246575342465748</v>
+      </c>
+      <c r="AN24" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>1y</v>
+      </c>
+      <c r="AO24">
+        <v>95.033000000000001</v>
+      </c>
+      <c r="AP24">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="25" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>205</v>
       </c>
@@ -6430,8 +6879,26 @@
       <c r="AK25" t="s">
         <v>60</v>
       </c>
+      <c r="AL25" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM25" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.7397260273972603E-3</v>
+      </c>
+      <c r="AN25" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>0y</v>
+      </c>
+      <c r="AO25">
+        <v>99.977000000000004</v>
+      </c>
+      <c r="AP25">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="26" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>210</v>
       </c>
@@ -6540,8 +7007,26 @@
       <c r="AK26" t="s">
         <v>60</v>
       </c>
+      <c r="AL26" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>696</v>
+      </c>
+      <c r="AM26" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.9068493150684931</v>
+      </c>
+      <c r="AN26" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2y</v>
+      </c>
+      <c r="AO26">
+        <v>79.686999999999998</v>
+      </c>
+      <c r="AP26">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="27" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>215</v>
       </c>
@@ -6650,8 +7135,26 @@
       <c r="AK27" t="s">
         <v>99</v>
       </c>
+      <c r="AL27" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>-17</v>
+      </c>
+      <c r="AM27" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>-4.6575342465753428E-2</v>
+      </c>
+      <c r="AN27" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>0y</v>
+      </c>
+      <c r="AO27" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP27">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="28" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>220</v>
       </c>
@@ -6760,8 +7263,26 @@
       <c r="AK28" t="s">
         <v>60</v>
       </c>
+      <c r="AL28" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>584</v>
+      </c>
+      <c r="AM28" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.6</v>
+      </c>
+      <c r="AN28" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2y</v>
+      </c>
+      <c r="AO28">
+        <v>95.611999999999995</v>
+      </c>
+      <c r="AP28">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="29" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>226</v>
       </c>
@@ -6870,8 +7391,26 @@
       <c r="AK29" t="s">
         <v>60</v>
       </c>
+      <c r="AL29" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>571</v>
+      </c>
+      <c r="AM29" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.5643835616438355</v>
+      </c>
+      <c r="AN29" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2y</v>
+      </c>
+      <c r="AO29">
+        <v>95.32</v>
+      </c>
+      <c r="AP29">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="30" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>232</v>
       </c>
@@ -6980,8 +7519,26 @@
       <c r="AK30" t="s">
         <v>60</v>
       </c>
+      <c r="AL30" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>4882</v>
+      </c>
+      <c r="AM30" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>13.375342465753425</v>
+      </c>
+      <c r="AN30" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>13y</v>
+      </c>
+      <c r="AO30">
+        <v>23.609000000000002</v>
+      </c>
+      <c r="AP30">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="31" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>237</v>
       </c>
@@ -7090,8 +7647,26 @@
       <c r="AK31" t="s">
         <v>60</v>
       </c>
+      <c r="AL31" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="AM31" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.6027397260273974</v>
+      </c>
+      <c r="AN31" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>3y</v>
+      </c>
+      <c r="AO31">
+        <v>86.921999999999997</v>
+      </c>
+      <c r="AP31">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="32" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>243</v>
       </c>
@@ -7200,8 +7775,26 @@
       <c r="AK32" t="s">
         <v>89</v>
       </c>
+      <c r="AL32" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>2828</v>
+      </c>
+      <c r="AM32" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>7.7479452054794518</v>
+      </c>
+      <c r="AN32" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>8y</v>
+      </c>
+      <c r="AO32">
+        <v>37.564</v>
+      </c>
+      <c r="AP32">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>249</v>
       </c>
@@ -7310,8 +7903,26 @@
       <c r="AK33" t="s">
         <v>60</v>
       </c>
+      <c r="AL33" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AM33" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>4.6575342465753428E-2</v>
+      </c>
+      <c r="AN33" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>0y</v>
+      </c>
+      <c r="AO33">
+        <v>99.561000000000007</v>
+      </c>
+      <c r="AP33">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>255</v>
       </c>
@@ -7420,8 +8031,26 @@
       <c r="AK34" t="s">
         <v>60</v>
       </c>
+      <c r="AL34" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>1300</v>
+      </c>
+      <c r="AM34" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>3.5616438356164384</v>
+      </c>
+      <c r="AN34" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>4y</v>
+      </c>
+      <c r="AO34">
+        <v>66.399000000000001</v>
+      </c>
+      <c r="AP34">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>260</v>
       </c>
@@ -7530,8 +8159,26 @@
       <c r="AK35" t="s">
         <v>121</v>
       </c>
+      <c r="AL35" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>2235</v>
+      </c>
+      <c r="AM35" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>6.1232876712328768</v>
+      </c>
+      <c r="AN35" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>6y</v>
+      </c>
+      <c r="AO35">
+        <v>82.543000000000006</v>
+      </c>
+      <c r="AP35">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="36" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>266</v>
       </c>
@@ -7640,8 +8287,26 @@
       <c r="AK36" t="s">
         <v>60</v>
       </c>
+      <c r="AL36" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>1662</v>
+      </c>
+      <c r="AM36" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>4.5534246575342463</v>
+      </c>
+      <c r="AN36" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>5y</v>
+      </c>
+      <c r="AO36">
+        <v>97.882000000000005</v>
+      </c>
+      <c r="AP36">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>269</v>
       </c>
@@ -7750,8 +8415,26 @@
       <c r="AK37" t="s">
         <v>60</v>
       </c>
+      <c r="AL37" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>442</v>
+      </c>
+      <c r="AM37" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.210958904109589</v>
+      </c>
+      <c r="AN37" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>1y</v>
+      </c>
+      <c r="AO37">
+        <v>87.28</v>
+      </c>
+      <c r="AP37">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>275</v>
       </c>
@@ -7860,8 +8543,26 @@
       <c r="AK38" t="s">
         <v>60</v>
       </c>
+      <c r="AL38" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>862</v>
+      </c>
+      <c r="AM38" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.3616438356164382</v>
+      </c>
+      <c r="AN38" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2y</v>
+      </c>
+      <c r="AO38">
+        <v>95.234999999999999</v>
+      </c>
+      <c r="AP38">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>281</v>
       </c>
@@ -7970,8 +8671,26 @@
       <c r="AK39" t="s">
         <v>289</v>
       </c>
+      <c r="AL39" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>2074</v>
+      </c>
+      <c r="AM39" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>5.6821917808219178</v>
+      </c>
+      <c r="AN39" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>6y</v>
+      </c>
+      <c r="AO39">
+        <v>77.923000000000002</v>
+      </c>
+      <c r="AP39">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>290</v>
       </c>
@@ -8080,8 +8799,26 @@
       <c r="AK40" t="s">
         <v>89</v>
       </c>
+      <c r="AL40" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>1654</v>
+      </c>
+      <c r="AM40" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>4.5315068493150683</v>
+      </c>
+      <c r="AN40" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>5y</v>
+      </c>
+      <c r="AO40">
+        <v>86.162000000000006</v>
+      </c>
+      <c r="AP40">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>296</v>
       </c>
@@ -8190,8 +8927,26 @@
       <c r="AK41" t="s">
         <v>60</v>
       </c>
+      <c r="AL41" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>367</v>
+      </c>
+      <c r="AM41" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.0054794520547945</v>
+      </c>
+      <c r="AN41" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>1y</v>
+      </c>
+      <c r="AO41">
+        <v>87.322000000000003</v>
+      </c>
+      <c r="AP41">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>301</v>
       </c>
@@ -8300,8 +9055,26 @@
       <c r="AK42" t="s">
         <v>60</v>
       </c>
+      <c r="AL42" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>205</v>
+      </c>
+      <c r="AM42" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.56164383561643838</v>
+      </c>
+      <c r="AN42" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>1y</v>
+      </c>
+      <c r="AO42">
+        <v>97.518000000000001</v>
+      </c>
+      <c r="AP42">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>307</v>
       </c>
@@ -8410,8 +9183,26 @@
       <c r="AK43" t="s">
         <v>289</v>
       </c>
+      <c r="AL43" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>1456</v>
+      </c>
+      <c r="AM43" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>3.989041095890411</v>
+      </c>
+      <c r="AN43" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>4y</v>
+      </c>
+      <c r="AO43">
+        <v>97.578999999999994</v>
+      </c>
+      <c r="AP43">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>314</v>
       </c>
@@ -8520,8 +9311,26 @@
       <c r="AK44" t="s">
         <v>143</v>
       </c>
+      <c r="AL44" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>3263</v>
+      </c>
+      <c r="AM44" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>8.9397260273972599</v>
+      </c>
+      <c r="AN44" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>9y</v>
+      </c>
+      <c r="AO44">
+        <v>35.82</v>
+      </c>
+      <c r="AP44">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>319</v>
       </c>
@@ -8630,8 +9439,26 @@
       <c r="AK45" t="s">
         <v>60</v>
       </c>
+      <c r="AL45" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>198</v>
+      </c>
+      <c r="AM45" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.54246575342465753</v>
+      </c>
+      <c r="AN45" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>1y</v>
+      </c>
+      <c r="AO45">
+        <v>98.519000000000005</v>
+      </c>
+      <c r="AP45">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>325</v>
       </c>
@@ -8740,8 +9567,26 @@
       <c r="AK46" t="s">
         <v>60</v>
       </c>
+      <c r="AL46" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>871</v>
+      </c>
+      <c r="AM46" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.3863013698630136</v>
+      </c>
+      <c r="AN46" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2y</v>
+      </c>
+      <c r="AO46">
+        <v>75.546999999999997</v>
+      </c>
+      <c r="AP46">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>331</v>
       </c>
@@ -8850,8 +9695,26 @@
       <c r="AK47" t="s">
         <v>143</v>
       </c>
+      <c r="AL47" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>1849</v>
+      </c>
+      <c r="AM47" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>5.065753424657534</v>
+      </c>
+      <c r="AN47" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>5y</v>
+      </c>
+      <c r="AO47">
+        <v>55.167000000000002</v>
+      </c>
+      <c r="AP47">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>336</v>
       </c>
@@ -8960,8 +9823,26 @@
       <c r="AK48" t="s">
         <v>121</v>
       </c>
+      <c r="AL48" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>274</v>
+      </c>
+      <c r="AM48" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.75068493150684934</v>
+      </c>
+      <c r="AN48" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>1y</v>
+      </c>
+      <c r="AO48">
+        <v>97.597999999999999</v>
+      </c>
+      <c r="AP48">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="49" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>342</v>
       </c>
@@ -9070,8 +9951,26 @@
       <c r="AK49" t="s">
         <v>89</v>
       </c>
+      <c r="AL49" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>982</v>
+      </c>
+      <c r="AM49" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.6904109589041094</v>
+      </c>
+      <c r="AN49" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>3y</v>
+      </c>
+      <c r="AO49">
+        <v>73.364999999999995</v>
+      </c>
+      <c r="AP49">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="50" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>347</v>
       </c>
@@ -9180,8 +10079,26 @@
       <c r="AK50" t="s">
         <v>60</v>
       </c>
+      <c r="AL50" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>282</v>
+      </c>
+      <c r="AM50" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.77260273972602744</v>
+      </c>
+      <c r="AN50" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>1y</v>
+      </c>
+      <c r="AO50">
+        <v>90.355000000000004</v>
+      </c>
+      <c r="AP50">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="51" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>352</v>
       </c>
@@ -9290,8 +10207,26 @@
       <c r="AK51" t="s">
         <v>60</v>
       </c>
+      <c r="AL51" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>1885</v>
+      </c>
+      <c r="AM51" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>5.1643835616438354</v>
+      </c>
+      <c r="AN51" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>5y</v>
+      </c>
+      <c r="AO51">
+        <v>54.987000000000002</v>
+      </c>
+      <c r="AP51">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="52" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>357</v>
       </c>
@@ -9400,8 +10335,26 @@
       <c r="AK52" t="s">
         <v>289</v>
       </c>
+      <c r="AL52" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>2235</v>
+      </c>
+      <c r="AM52" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>6.1232876712328768</v>
+      </c>
+      <c r="AN52" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>6y</v>
+      </c>
+      <c r="AO52">
+        <v>81.403999999999996</v>
+      </c>
+      <c r="AP52">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="53" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>360</v>
       </c>
@@ -9510,8 +10463,26 @@
       <c r="AK53" t="s">
         <v>143</v>
       </c>
+      <c r="AL53" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>276</v>
+      </c>
+      <c r="AM53" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.75616438356164384</v>
+      </c>
+      <c r="AN53" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>1y</v>
+      </c>
+      <c r="AO53">
+        <v>90.566000000000003</v>
+      </c>
+      <c r="AP53">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="54" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>365</v>
       </c>
@@ -9620,8 +10591,26 @@
       <c r="AK54" t="s">
         <v>60</v>
       </c>
+      <c r="AL54" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>2206</v>
+      </c>
+      <c r="AM54" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>6.043835616438356</v>
+      </c>
+      <c r="AN54" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>6y</v>
+      </c>
+      <c r="AO54">
+        <v>81.875</v>
+      </c>
+      <c r="AP54">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="55" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>371</v>
       </c>
@@ -9730,8 +10719,26 @@
       <c r="AK55" t="s">
         <v>143</v>
       </c>
+      <c r="AL55" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>128</v>
+      </c>
+      <c r="AM55" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.35068493150684932</v>
+      </c>
+      <c r="AN55" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>0y</v>
+      </c>
+      <c r="AO55">
+        <v>98.064999999999998</v>
+      </c>
+      <c r="AP55">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="56" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>377</v>
       </c>
@@ -9840,8 +10847,26 @@
       <c r="AK56" t="s">
         <v>289</v>
       </c>
+      <c r="AL56" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>2143</v>
+      </c>
+      <c r="AM56" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>5.8712328767123285</v>
+      </c>
+      <c r="AN56" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>6y</v>
+      </c>
+      <c r="AO56">
+        <v>80.682000000000002</v>
+      </c>
+      <c r="AP56">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="57" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>383</v>
       </c>
@@ -9950,8 +10975,26 @@
       <c r="AK57" t="s">
         <v>60</v>
       </c>
+      <c r="AL57" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>197</v>
+      </c>
+      <c r="AM57" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.53972602739726028</v>
+      </c>
+      <c r="AN57" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>1y</v>
+      </c>
+      <c r="AO57" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP57">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="58" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>395</v>
       </c>
@@ -10060,8 +11103,26 @@
       <c r="AK58" t="s">
         <v>60</v>
       </c>
+      <c r="AL58" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>134</v>
+      </c>
+      <c r="AM58" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.36712328767123287</v>
+      </c>
+      <c r="AN58" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>0y</v>
+      </c>
+      <c r="AO58" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP58">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="59" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>400</v>
       </c>
@@ -10170,8 +11231,26 @@
       <c r="AK59" t="s">
         <v>394</v>
       </c>
+      <c r="AL59" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>343</v>
+      </c>
+      <c r="AM59" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.9397260273972603</v>
+      </c>
+      <c r="AN59" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>1y</v>
+      </c>
+      <c r="AO59" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP59">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="60" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>403</v>
       </c>
@@ -10280,8 +11359,26 @@
       <c r="AK60" t="s">
         <v>60</v>
       </c>
+      <c r="AL60" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>838</v>
+      </c>
+      <c r="AM60" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.2958904109589042</v>
+      </c>
+      <c r="AN60" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2y</v>
+      </c>
+      <c r="AO60">
+        <v>75.802000000000007</v>
+      </c>
+      <c r="AP60">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="61" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>408</v>
       </c>
@@ -10390,8 +11487,26 @@
       <c r="AK61" t="s">
         <v>143</v>
       </c>
+      <c r="AL61" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>3055</v>
+      </c>
+      <c r="AM61" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>8.3698630136986303</v>
+      </c>
+      <c r="AN61" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>8y</v>
+      </c>
+      <c r="AO61">
+        <v>81.733999999999995</v>
+      </c>
+      <c r="AP61">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="62" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>414</v>
       </c>
@@ -10500,8 +11615,26 @@
       <c r="AK62" t="s">
         <v>60</v>
       </c>
+      <c r="AL62" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>880</v>
+      </c>
+      <c r="AM62" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.4109589041095889</v>
+      </c>
+      <c r="AN62" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2y</v>
+      </c>
+      <c r="AO62">
+        <v>74.078000000000003</v>
+      </c>
+      <c r="AP62">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="63" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>419</v>
       </c>
@@ -10610,8 +11743,26 @@
       <c r="AK63" t="s">
         <v>60</v>
       </c>
+      <c r="AL63" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>87</v>
+      </c>
+      <c r="AM63" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.23835616438356164</v>
+      </c>
+      <c r="AN63" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>0y</v>
+      </c>
+      <c r="AO63">
+        <v>97.054000000000002</v>
+      </c>
+      <c r="AP63">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="64" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>424</v>
       </c>
@@ -10720,8 +11871,26 @@
       <c r="AK64" t="s">
         <v>143</v>
       </c>
+      <c r="AL64" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>374</v>
+      </c>
+      <c r="AM64" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.0246575342465754</v>
+      </c>
+      <c r="AN64" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>1y</v>
+      </c>
+      <c r="AO64">
+        <v>97.043999999999997</v>
+      </c>
+      <c r="AP64">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>430</v>
       </c>
@@ -10830,8 +11999,26 @@
       <c r="AK65" t="s">
         <v>60</v>
       </c>
+      <c r="AL65" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>1153</v>
+      </c>
+      <c r="AM65" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>3.1589041095890411</v>
+      </c>
+      <c r="AN65" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>3y</v>
+      </c>
+      <c r="AO65">
+        <v>88.266999999999996</v>
+      </c>
+      <c r="AP65">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>436</v>
       </c>
@@ -10940,8 +12127,26 @@
       <c r="AK66" t="s">
         <v>60</v>
       </c>
+      <c r="AL66" s="5">
+        <f t="shared" ca="1" si="0"/>
+        <v>-4</v>
+      </c>
+      <c r="AM66" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>-1.0958904109589041E-2</v>
+      </c>
+      <c r="AN66" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>0y</v>
+      </c>
+      <c r="AO66" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP66">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>442</v>
       </c>
@@ -11050,8 +12255,26 @@
       <c r="AK67" t="s">
         <v>394</v>
       </c>
+      <c r="AL67" s="5">
+        <f t="shared" ref="AL67:AL70" ca="1" si="3">G67-$AQ$2</f>
+        <v>395</v>
+      </c>
+      <c r="AM67" s="3">
+        <f t="shared" ref="AM67:AM70" ca="1" si="4">AL67/365</f>
+        <v>1.0821917808219179</v>
+      </c>
+      <c r="AN67" t="str">
+        <f t="shared" ref="AN67:AN70" ca="1" si="5">IF(AM67&gt;36,"&gt;36y",ROUND(AM67,0)&amp;"y")</f>
+        <v>1y</v>
+      </c>
+      <c r="AO67" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP67">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
         <v>447</v>
       </c>
@@ -11160,8 +12383,26 @@
       <c r="AK68" t="s">
         <v>289</v>
       </c>
+      <c r="AL68" s="5">
+        <f t="shared" ca="1" si="3"/>
+        <v>2283</v>
+      </c>
+      <c r="AM68" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>6.2547945205479456</v>
+      </c>
+      <c r="AN68" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>6y</v>
+      </c>
+      <c r="AO68">
+        <v>87.180999999999997</v>
+      </c>
+      <c r="AP68">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>453</v>
       </c>
@@ -11270,8 +12511,26 @@
       <c r="AK69" t="s">
         <v>143</v>
       </c>
+      <c r="AL69" s="5">
+        <f t="shared" ca="1" si="3"/>
+        <v>1157</v>
+      </c>
+      <c r="AM69" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>3.1698630136986301</v>
+      </c>
+      <c r="AN69" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>3y</v>
+      </c>
+      <c r="AO69">
+        <v>68.972999999999999</v>
+      </c>
+      <c r="AP69">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
         <v>458</v>
       </c>
@@ -11379,6 +12638,24 @@
       </c>
       <c r="AK70" t="s">
         <v>143</v>
+      </c>
+      <c r="AL70" s="5">
+        <f t="shared" ca="1" si="3"/>
+        <v>695</v>
+      </c>
+      <c r="AM70" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>1.904109589041096</v>
+      </c>
+      <c r="AN70" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>2y</v>
+      </c>
+      <c r="AO70">
+        <v>94.644000000000005</v>
+      </c>
+      <c r="AP70">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>

--- a/datos_y_modelos/Domestic/supra.xlsx
+++ b/datos_y_modelos/Domestic/supra.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bloomberglp-my.sharepoint.com/personal/tsiqueira4_bloomberg_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bloomberglp-my.sharepoint.com/personal/tsiqueira4_bloomberg_com/Documents/Desktop/master_thesis_economics/datos_y_modelos/Domestic/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98CE6E99-448D-4B37-B3BD-6030979350D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A6F68A9-FCC5-4E77-BF6D-576ACF924730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-70" yWindow="10690" windowWidth="19420" windowHeight="11620" xr2:uid="{EC0627F6-2DC6-4AF1-9A23-F0938631E874}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EC0627F6-2DC6-4AF1-9A23-F0938631E874}"/>
   </bookViews>
   <sheets>
     <sheet name="db_values_only" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">db_values_only!$B$1:$AK$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">db_values_only!$B$1:$AQ$64</definedName>
     <definedName name="_INH">'[1]Estimates Break Down'!$Y$1</definedName>
     <definedName name="bb_Mzk0MjlDQUYwQjg5NEJCM0" hidden="1">#REF!</definedName>
     <definedName name="bb_RjdDN0M0MkE1NDhCNEQyNj" hidden="1">#REF!</definedName>
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2027" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1836" uniqueCount="433">
   <si>
     <t>id</t>
   </si>
@@ -769,21 +769,6 @@
     <t>5/26/2027</t>
   </si>
   <si>
-    <t>BJ768151 Corp</t>
-  </si>
-  <si>
-    <t>BBG00V4VDW67</t>
-  </si>
-  <si>
-    <t>XS2183142798</t>
-  </si>
-  <si>
-    <t>6/12/2020</t>
-  </si>
-  <si>
-    <t>6/12/2025</t>
-  </si>
-  <si>
     <t>ZM636659 Corp</t>
   </si>
   <si>
@@ -1273,66 +1258,6 @@
     <t>5/12/2022</t>
   </si>
   <si>
-    <t>BN542084 Corp</t>
-  </si>
-  <si>
-    <t>BBG00YXRQ0N5</t>
-  </si>
-  <si>
-    <t>XS2289821568</t>
-  </si>
-  <si>
-    <t>1/12/2026</t>
-  </si>
-  <si>
-    <t>AAAp</t>
-  </si>
-  <si>
-    <t>1/13/2022</t>
-  </si>
-  <si>
-    <t>CORP ANDINA DE FOMENTO</t>
-  </si>
-  <si>
-    <t>6/7/2021</t>
-  </si>
-  <si>
-    <t>190458Z VC</t>
-  </si>
-  <si>
-    <t>Domestic</t>
-  </si>
-  <si>
-    <t>VC</t>
-  </si>
-  <si>
-    <t>Corporacion Andina de Fomento (CAF) operates as a development bank for Latin Americans and the Caribbeans. The Bank provides loans, credit operations, and non-refundable funds for development of water and sanitation, energy, road infrastructure, productive transformation, and urban mobility infrastructure. CAF serves customers in Latin America, the Caribbean, Spain, and Portugal.</t>
-  </si>
-  <si>
-    <t>BQ721132 Corp</t>
-  </si>
-  <si>
-    <t>BBG011Y5N4C0</t>
-  </si>
-  <si>
-    <t>XS2251370727</t>
-  </si>
-  <si>
-    <t>11/10/2020</t>
-  </si>
-  <si>
-    <t>11/10/2025</t>
-  </si>
-  <si>
-    <t>BP780031 Corp</t>
-  </si>
-  <si>
-    <t>BBG0116Z35F1</t>
-  </si>
-  <si>
-    <t>6/7/2026</t>
-  </si>
-  <si>
     <t>ZS021650 Corp</t>
   </si>
   <si>
@@ -1430,39 +1355,6 @@
   </si>
   <si>
     <t>2/25/2024</t>
-  </si>
-  <si>
-    <t>ZK956370 Corp</t>
-  </si>
-  <si>
-    <t>BBG01GZVW8T2</t>
-  </si>
-  <si>
-    <t>XS1247879049</t>
-  </si>
-  <si>
-    <t>6/25/2015</t>
-  </si>
-  <si>
-    <t>6/25/2025</t>
-  </si>
-  <si>
-    <t>12/25/2015</t>
-  </si>
-  <si>
-    <t>BQ706131 Corp</t>
-  </si>
-  <si>
-    <t>BBG011XWZVD8</t>
-  </si>
-  <si>
-    <t>XS2369569624</t>
-  </si>
-  <si>
-    <t>7/29/2021</t>
-  </si>
-  <si>
-    <t>7/29/2026</t>
   </si>
   <si>
     <t>BR425633 Corp</t>
@@ -1537,7 +1429,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -1592,7 +1484,7 @@
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3661,7 +3553,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E3BFF2A-B712-459A-8265-CC1EA8C41DE6}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="B1:AQ70"/>
+  <dimension ref="B1:AQ64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -3807,19 +3699,19 @@
         <v>35</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>464</v>
+        <v>428</v>
       </c>
       <c r="AM1" s="3" t="s">
-        <v>465</v>
+        <v>429</v>
       </c>
       <c r="AO1" t="s">
-        <v>466</v>
+        <v>430</v>
       </c>
       <c r="AP1" t="s">
-        <v>467</v>
+        <v>431</v>
       </c>
       <c r="AQ1" t="s">
-        <v>468</v>
+        <v>432</v>
       </c>
     </row>
     <row r="2" spans="2:43" x14ac:dyDescent="0.25">
@@ -3933,11 +3825,11 @@
       </c>
       <c r="AL2" s="5">
         <f ca="1">G2-$AQ$2</f>
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM2" s="3">
         <f ca="1">AL2/365</f>
-        <v>0.56712328767123288</v>
+        <v>0.56438356164383563</v>
       </c>
       <c r="AN2" t="str">
         <f ca="1">IF(AM2&gt;36,"&gt;36y",ROUND(AM2,0)&amp;"y")</f>
@@ -3951,7 +3843,7 @@
       </c>
       <c r="AQ2" s="4">
         <f ca="1">TODAY()</f>
-        <v>45837</v>
+        <v>45838</v>
       </c>
     </row>
     <row r="3" spans="2:43" x14ac:dyDescent="0.25">
@@ -4064,15 +3956,15 @@
         <v>60</v>
       </c>
       <c r="AL3" s="5">
-        <f t="shared" ref="AL3:AL66" ca="1" si="0">G3-$AQ$2</f>
-        <v>961</v>
+        <f t="shared" ref="AL3:AL61" ca="1" si="0">G3-$AQ$2</f>
+        <v>960</v>
       </c>
       <c r="AM3" s="3">
-        <f t="shared" ref="AM3:AM66" ca="1" si="1">AL3/365</f>
-        <v>2.6328767123287671</v>
+        <f t="shared" ref="AM3:AM61" ca="1" si="1">AL3/365</f>
+        <v>2.6301369863013697</v>
       </c>
       <c r="AN3" t="str">
-        <f t="shared" ref="AN3:AN66" ca="1" si="2">IF(AM3&gt;36,"&gt;36y",ROUND(AM3,0)&amp;"y")</f>
+        <f t="shared" ref="AN3:AN61" ca="1" si="2">IF(AM3&gt;36,"&gt;36y",ROUND(AM3,0)&amp;"y")</f>
         <v>3y</v>
       </c>
       <c r="AO3">
@@ -4193,11 +4085,11 @@
       </c>
       <c r="AL4" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="AM4" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>3.6191780821917807</v>
+        <v>3.6164383561643834</v>
       </c>
       <c r="AN4" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4321,11 +4213,11 @@
       </c>
       <c r="AL5" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>4607</v>
+        <v>4606</v>
       </c>
       <c r="AM5" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>12.621917808219179</v>
+        <v>12.61917808219178</v>
       </c>
       <c r="AN5" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4449,11 +4341,11 @@
       </c>
       <c r="AL6" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="AM6" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>6.6</v>
+        <v>6.5972602739726032</v>
       </c>
       <c r="AN6" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4577,11 +4469,11 @@
       </c>
       <c r="AL7" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AM7" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5835616438356164</v>
+        <v>1.5808219178082192</v>
       </c>
       <c r="AN7" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4705,11 +4597,11 @@
       </c>
       <c r="AL8" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="AM8" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>6.2821917808219174</v>
+        <v>6.279452054794521</v>
       </c>
       <c r="AN8" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4833,11 +4725,11 @@
       </c>
       <c r="AL9" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>5720</v>
+        <v>5719</v>
       </c>
       <c r="AM9" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>15.671232876712329</v>
+        <v>15.668493150684931</v>
       </c>
       <c r="AN9" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4961,11 +4853,11 @@
       </c>
       <c r="AL10" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AM10" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.60547945205479448</v>
+        <v>0.60273972602739723</v>
       </c>
       <c r="AN10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5089,11 +4981,11 @@
       </c>
       <c r="AL11" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AM11" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>1.2547945205479452</v>
+        <v>1.252054794520548</v>
       </c>
       <c r="AN11" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5217,11 +5109,11 @@
       </c>
       <c r="AL12" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AM12" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.33424657534246577</v>
+        <v>0.33150684931506852</v>
       </c>
       <c r="AN12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5345,11 +5237,11 @@
       </c>
       <c r="AL13" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>6084</v>
+        <v>6083</v>
       </c>
       <c r="AM13" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>16.668493150684931</v>
+        <v>16.665753424657535</v>
       </c>
       <c r="AN13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5473,11 +5365,11 @@
       </c>
       <c r="AL14" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>3523</v>
+        <v>3522</v>
       </c>
       <c r="AM14" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>9.6520547945205486</v>
+        <v>9.6493150684931503</v>
       </c>
       <c r="AN14" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5601,11 +5493,11 @@
       </c>
       <c r="AL15" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="AM15" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>2.5452054794520547</v>
+        <v>2.5424657534246577</v>
       </c>
       <c r="AN15" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5729,11 +5621,11 @@
       </c>
       <c r="AL16" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>4349</v>
+        <v>4348</v>
       </c>
       <c r="AM16" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>11.915068493150685</v>
+        <v>11.912328767123288</v>
       </c>
       <c r="AN16" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5857,11 +5749,11 @@
       </c>
       <c r="AL17" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="AM17" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>2.8904109589041096</v>
+        <v>2.8876712328767122</v>
       </c>
       <c r="AN17" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5985,11 +5877,11 @@
       </c>
       <c r="AL18" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="AM18" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>4.8931506849315065</v>
+        <v>4.8904109589041092</v>
       </c>
       <c r="AN18" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -6113,11 +6005,11 @@
       </c>
       <c r="AL19" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="AM19" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>4.5534246575342463</v>
+        <v>4.5506849315068489</v>
       </c>
       <c r="AN19" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -6241,11 +6133,11 @@
       </c>
       <c r="AL20" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>2818</v>
+        <v>2817</v>
       </c>
       <c r="AM20" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>7.720547945205479</v>
+        <v>7.7178082191780826</v>
       </c>
       <c r="AN20" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -6369,11 +6261,11 @@
       </c>
       <c r="AL21" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="AM21" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>4.1643835616438354</v>
+        <v>4.161643835616438</v>
       </c>
       <c r="AN21" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -6497,11 +6389,11 @@
       </c>
       <c r="AL22" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="AM22" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>4.3041095890410963</v>
+        <v>4.3013698630136989</v>
       </c>
       <c r="AN22" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -6625,11 +6517,11 @@
       </c>
       <c r="AL23" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>4643</v>
+        <v>4642</v>
       </c>
       <c r="AM23" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>12.72054794520548</v>
+        <v>12.717808219178082</v>
       </c>
       <c r="AN23" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -6753,11 +6645,11 @@
       </c>
       <c r="AL24" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AM24" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74246575342465748</v>
+        <v>0.73972602739726023</v>
       </c>
       <c r="AN24" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -6881,11 +6773,11 @@
       </c>
       <c r="AL25" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM25" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>2.7397260273972603E-3</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -7009,11 +6901,11 @@
       </c>
       <c r="AL26" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="AM26" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>1.9068493150684931</v>
+        <v>1.904109589041096</v>
       </c>
       <c r="AN26" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -7031,7 +6923,7 @@
         <v>215</v>
       </c>
       <c r="C27" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="D27" t="s">
         <v>216</v>
@@ -7049,10 +6941,10 @@
         <v>42</v>
       </c>
       <c r="I27" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K27" t="s">
         <v>44</v>
@@ -7076,25 +6968,25 @@
         <v>48</v>
       </c>
       <c r="R27" t="s">
-        <v>47</v>
-      </c>
-      <c r="S27" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="S27">
+        <v>1</v>
       </c>
       <c r="T27">
-        <v>-117.01410018065168</v>
+        <v>-99.532939063142038</v>
       </c>
       <c r="U27">
-        <v>13.443358999999999</v>
+        <v>13.020818999999999</v>
       </c>
       <c r="V27">
-        <v>0</v>
-      </c>
-      <c r="W27" t="s">
-        <v>49</v>
+        <v>4</v>
+      </c>
+      <c r="W27">
+        <v>290000</v>
       </c>
       <c r="X27" t="s">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="Y27" t="s">
         <v>51</v>
@@ -7112,16 +7004,16 @@
         <v>55</v>
       </c>
       <c r="AD27" t="s">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="AE27" t="s">
         <v>57</v>
       </c>
       <c r="AF27">
-        <v>500000000</v>
+        <v>300000000</v>
       </c>
       <c r="AG27">
-        <v>500000000</v>
+        <v>300000000</v>
       </c>
       <c r="AH27" t="s">
         <v>58</v>
@@ -7130,25 +7022,25 @@
         <v>49</v>
       </c>
       <c r="AJ27" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="AK27" t="s">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="AL27" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>-17</v>
+        <v>583</v>
       </c>
       <c r="AM27" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>-4.6575342465753428E-2</v>
+        <v>1.5972602739726027</v>
       </c>
       <c r="AN27" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>0y</v>
-      </c>
-      <c r="AO27" t="s">
-        <v>49</v>
+        <v>2y</v>
+      </c>
+      <c r="AO27">
+        <v>95.611999999999995</v>
       </c>
       <c r="AP27">
         <v>1000</v>
@@ -7156,22 +7048,22 @@
     </row>
     <row r="28" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C28" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="D28" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E28" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F28" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G28" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H28" t="s">
         <v>42</v>
@@ -7180,7 +7072,7 @@
         <v>43</v>
       </c>
       <c r="J28">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="K28" t="s">
         <v>44</v>
@@ -7210,16 +7102,16 @@
         <v>1</v>
       </c>
       <c r="T28">
-        <v>-99.532939063142038</v>
+        <v>-112.02839966616516</v>
       </c>
       <c r="U28">
-        <v>13.020818999999999</v>
+        <v>12.921078</v>
       </c>
       <c r="V28">
-        <v>4</v>
-      </c>
-      <c r="W28">
-        <v>290000</v>
+        <v>0</v>
+      </c>
+      <c r="W28" t="s">
+        <v>49</v>
       </c>
       <c r="X28" t="s">
         <v>50</v>
@@ -7240,16 +7132,16 @@
         <v>55</v>
       </c>
       <c r="AD28" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AE28" t="s">
         <v>57</v>
       </c>
       <c r="AF28">
-        <v>300000000</v>
+        <v>150000000</v>
       </c>
       <c r="AG28">
-        <v>300000000</v>
+        <v>150000000</v>
       </c>
       <c r="AH28" t="s">
         <v>58</v>
@@ -7265,18 +7157,18 @@
       </c>
       <c r="AL28" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>584</v>
+        <v>570</v>
       </c>
       <c r="AM28" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>1.6</v>
+        <v>1.5616438356164384</v>
       </c>
       <c r="AN28" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>2y</v>
       </c>
       <c r="AO28">
-        <v>95.611999999999995</v>
+        <v>95.32</v>
       </c>
       <c r="AP28">
         <v>1000</v>
@@ -7284,31 +7176,31 @@
     </row>
     <row r="29" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C29" t="s">
         <v>37</v>
       </c>
       <c r="D29" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E29" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F29" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G29" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H29" t="s">
         <v>42</v>
       </c>
       <c r="I29" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="J29">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="K29" t="s">
         <v>44</v>
@@ -7334,14 +7226,14 @@
       <c r="R29" t="s">
         <v>49</v>
       </c>
-      <c r="S29">
-        <v>1</v>
+      <c r="S29" t="s">
+        <v>44</v>
       </c>
       <c r="T29">
-        <v>-112.02839966616516</v>
+        <v>-241.61272115915241</v>
       </c>
       <c r="U29">
-        <v>12.921078</v>
+        <v>11.602073000000001</v>
       </c>
       <c r="V29">
         <v>0</v>
@@ -7368,16 +7260,16 @@
         <v>55</v>
       </c>
       <c r="AD29" t="s">
-        <v>231</v>
+        <v>44</v>
       </c>
       <c r="AE29" t="s">
         <v>57</v>
       </c>
       <c r="AF29">
-        <v>150000000</v>
+        <v>1200000000</v>
       </c>
       <c r="AG29">
-        <v>150000000</v>
+        <v>1200000000</v>
       </c>
       <c r="AH29" t="s">
         <v>58</v>
@@ -7393,18 +7285,18 @@
       </c>
       <c r="AL29" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>571</v>
+        <v>4881</v>
       </c>
       <c r="AM29" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5643835616438355</v>
+        <v>13.372602739726027</v>
       </c>
       <c r="AN29" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>2y</v>
+        <v>13y</v>
       </c>
       <c r="AO29">
-        <v>95.32</v>
+        <v>23.609000000000002</v>
       </c>
       <c r="AP29">
         <v>1000</v>
@@ -7415,7 +7307,7 @@
         <v>232</v>
       </c>
       <c r="C30" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="D30" t="s">
         <v>233</v>
@@ -7433,10 +7325,10 @@
         <v>42</v>
       </c>
       <c r="I30" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="K30" t="s">
         <v>44</v>
@@ -7462,14 +7354,14 @@
       <c r="R30" t="s">
         <v>49</v>
       </c>
-      <c r="S30" t="s">
-        <v>44</v>
+      <c r="S30">
+        <v>1</v>
       </c>
       <c r="T30">
-        <v>-241.61272115915241</v>
+        <v>-111.37445286202254</v>
       </c>
       <c r="U30">
-        <v>11.602073000000001</v>
+        <v>12.491676</v>
       </c>
       <c r="V30">
         <v>0</v>
@@ -7496,16 +7388,16 @@
         <v>55</v>
       </c>
       <c r="AD30" t="s">
-        <v>44</v>
+        <v>237</v>
       </c>
       <c r="AE30" t="s">
         <v>57</v>
       </c>
       <c r="AF30">
-        <v>1200000000</v>
+        <v>200000000</v>
       </c>
       <c r="AG30">
-        <v>1200000000</v>
+        <v>200000000</v>
       </c>
       <c r="AH30" t="s">
         <v>58</v>
@@ -7521,18 +7413,18 @@
       </c>
       <c r="AL30" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>4882</v>
+        <v>949</v>
       </c>
       <c r="AM30" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>13.375342465753425</v>
+        <v>2.6</v>
       </c>
       <c r="AN30" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>13y</v>
+        <v>3y</v>
       </c>
       <c r="AO30">
-        <v>23.609000000000002</v>
+        <v>86.921999999999997</v>
       </c>
       <c r="AP30">
         <v>1000</v>
@@ -7540,31 +7432,31 @@
     </row>
     <row r="31" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C31" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="D31" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E31" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F31" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G31" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H31" t="s">
         <v>42</v>
       </c>
       <c r="I31" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="J31">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="K31" t="s">
         <v>44</v>
@@ -7590,14 +7482,14 @@
       <c r="R31" t="s">
         <v>49</v>
       </c>
-      <c r="S31">
-        <v>1</v>
+      <c r="S31" t="s">
+        <v>44</v>
       </c>
       <c r="T31">
-        <v>-111.37445286202254</v>
+        <v>-46.249759099704058</v>
       </c>
       <c r="U31">
-        <v>12.491676</v>
+        <v>13.4528</v>
       </c>
       <c r="V31">
         <v>0</v>
@@ -7606,7 +7498,7 @@
         <v>49</v>
       </c>
       <c r="X31" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="Y31" t="s">
         <v>51</v>
@@ -7618,22 +7510,22 @@
         <v>53</v>
       </c>
       <c r="AB31" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="AC31" t="s">
         <v>55</v>
       </c>
       <c r="AD31" t="s">
-        <v>242</v>
+        <v>44</v>
       </c>
       <c r="AE31" t="s">
-        <v>57</v>
+        <v>243</v>
       </c>
       <c r="AF31">
-        <v>200000000</v>
+        <v>320400400</v>
       </c>
       <c r="AG31">
-        <v>200000000</v>
+        <v>320400400</v>
       </c>
       <c r="AH31" t="s">
         <v>58</v>
@@ -7642,25 +7534,25 @@
         <v>49</v>
       </c>
       <c r="AJ31" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="AK31" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="AL31" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>950</v>
+        <v>2827</v>
       </c>
       <c r="AM31" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>2.6027397260273974</v>
+        <v>7.7452054794520544</v>
       </c>
       <c r="AN31" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>3y</v>
+        <v>8y</v>
       </c>
       <c r="AO31">
-        <v>86.921999999999997</v>
+        <v>37.564</v>
       </c>
       <c r="AP31">
         <v>1000</v>
@@ -7668,31 +7560,31 @@
     </row>
     <row r="32" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C32" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="D32" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E32" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F32" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G32" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H32" t="s">
         <v>42</v>
       </c>
       <c r="I32" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="K32" t="s">
         <v>44</v>
@@ -7718,14 +7610,14 @@
       <c r="R32" t="s">
         <v>49</v>
       </c>
-      <c r="S32" t="s">
-        <v>44</v>
+      <c r="S32">
+        <v>1</v>
       </c>
       <c r="T32">
-        <v>-46.249759099704058</v>
+        <v>-128.47137640354129</v>
       </c>
       <c r="U32">
-        <v>13.4528</v>
+        <v>13.328786000000001</v>
       </c>
       <c r="V32">
         <v>0</v>
@@ -7734,7 +7626,7 @@
         <v>49</v>
       </c>
       <c r="X32" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="Y32" t="s">
         <v>51</v>
@@ -7746,22 +7638,22 @@
         <v>53</v>
       </c>
       <c r="AB32" t="s">
-        <v>141</v>
+        <v>54</v>
       </c>
       <c r="AC32" t="s">
         <v>55</v>
       </c>
       <c r="AD32" t="s">
-        <v>44</v>
+        <v>249</v>
       </c>
       <c r="AE32" t="s">
-        <v>248</v>
+        <v>57</v>
       </c>
       <c r="AF32">
-        <v>320400400</v>
+        <v>200000000</v>
       </c>
       <c r="AG32">
-        <v>320400400</v>
+        <v>200000000</v>
       </c>
       <c r="AH32" t="s">
         <v>58</v>
@@ -7770,25 +7662,25 @@
         <v>49</v>
       </c>
       <c r="AJ32" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="AK32" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="AL32" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>2828</v>
+        <v>16</v>
       </c>
       <c r="AM32" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>7.7479452054794518</v>
+        <v>4.3835616438356165E-2</v>
       </c>
       <c r="AN32" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>8y</v>
+        <v>0y</v>
       </c>
       <c r="AO32">
-        <v>37.564</v>
+        <v>99.561000000000007</v>
       </c>
       <c r="AP32">
         <v>1000</v>
@@ -7796,31 +7688,31 @@
     </row>
     <row r="33" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C33" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="D33" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E33" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F33" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G33" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H33" t="s">
         <v>42</v>
       </c>
       <c r="I33" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="J33">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="K33" t="s">
         <v>44</v>
@@ -7846,14 +7738,14 @@
       <c r="R33" t="s">
         <v>49</v>
       </c>
-      <c r="S33">
-        <v>1</v>
+      <c r="S33" t="s">
+        <v>44</v>
       </c>
       <c r="T33">
-        <v>-128.47137640354129</v>
+        <v>-141.83869720471094</v>
       </c>
       <c r="U33">
-        <v>13.328786000000001</v>
+        <v>12.292020000000001</v>
       </c>
       <c r="V33">
         <v>0</v>
@@ -7880,16 +7772,16 @@
         <v>55</v>
       </c>
       <c r="AD33" t="s">
-        <v>254</v>
+        <v>44</v>
       </c>
       <c r="AE33" t="s">
         <v>57</v>
       </c>
       <c r="AF33">
-        <v>200000000</v>
+        <v>150000000</v>
       </c>
       <c r="AG33">
-        <v>200000000</v>
+        <v>57990000</v>
       </c>
       <c r="AH33" t="s">
         <v>58</v>
@@ -7905,18 +7797,18 @@
       </c>
       <c r="AL33" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>1299</v>
       </c>
       <c r="AM33" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>4.6575342465753428E-2</v>
+        <v>3.558904109589041</v>
       </c>
       <c r="AN33" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>0y</v>
+        <v>4y</v>
       </c>
       <c r="AO33">
-        <v>99.561000000000007</v>
+        <v>66.399000000000001</v>
       </c>
       <c r="AP33">
         <v>1000</v>
@@ -7927,7 +7819,7 @@
         <v>255</v>
       </c>
       <c r="C34" t="s">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="D34" t="s">
         <v>256</v>
@@ -7945,10 +7837,10 @@
         <v>42</v>
       </c>
       <c r="I34" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K34" t="s">
         <v>44</v>
@@ -7966,31 +7858,31 @@
         <v>44</v>
       </c>
       <c r="P34" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q34" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R34" t="s">
         <v>49</v>
       </c>
-      <c r="S34" t="s">
-        <v>44</v>
+      <c r="S34">
+        <v>1</v>
       </c>
       <c r="T34">
-        <v>-141.83869720471094</v>
+        <v>-139.07738104537214</v>
       </c>
       <c r="U34">
-        <v>12.292020000000001</v>
+        <v>12.569376</v>
       </c>
       <c r="V34">
-        <v>0</v>
-      </c>
-      <c r="W34" t="s">
-        <v>49</v>
+        <v>1</v>
+      </c>
+      <c r="W34">
+        <v>350000</v>
       </c>
       <c r="X34" t="s">
-        <v>50</v>
+        <v>117</v>
       </c>
       <c r="Y34" t="s">
         <v>51</v>
@@ -8008,16 +7900,16 @@
         <v>55</v>
       </c>
       <c r="AD34" t="s">
-        <v>44</v>
+        <v>260</v>
       </c>
       <c r="AE34" t="s">
         <v>57</v>
       </c>
       <c r="AF34">
-        <v>150000000</v>
+        <v>100000000</v>
       </c>
       <c r="AG34">
-        <v>57990000</v>
+        <v>100000000</v>
       </c>
       <c r="AH34" t="s">
         <v>58</v>
@@ -8026,25 +7918,25 @@
         <v>49</v>
       </c>
       <c r="AJ34" t="s">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="AK34" t="s">
-        <v>60</v>
+        <v>121</v>
       </c>
       <c r="AL34" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>1300</v>
+        <v>2234</v>
       </c>
       <c r="AM34" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>3.5616438356164384</v>
+        <v>6.1205479452054794</v>
       </c>
       <c r="AN34" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>4y</v>
+        <v>6y</v>
       </c>
       <c r="AO34">
-        <v>66.399000000000001</v>
+        <v>82.543000000000006</v>
       </c>
       <c r="AP34">
         <v>1000</v>
@@ -8052,22 +7944,22 @@
     </row>
     <row r="35" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C35" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="D35" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E35" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F35" t="s">
-        <v>263</v>
+        <v>173</v>
       </c>
       <c r="G35" t="s">
-        <v>264</v>
+        <v>174</v>
       </c>
       <c r="H35" t="s">
         <v>42</v>
@@ -8076,7 +7968,7 @@
         <v>43</v>
       </c>
       <c r="J35">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="K35" t="s">
         <v>44</v>
@@ -8094,10 +7986,10 @@
         <v>44</v>
       </c>
       <c r="P35" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R35" t="s">
         <v>49</v>
@@ -8106,19 +7998,19 @@
         <v>1</v>
       </c>
       <c r="T35">
-        <v>-139.07738104537214</v>
+        <v>-143.66753763761881</v>
       </c>
       <c r="U35">
-        <v>12.569376</v>
+        <v>12.362524000000001</v>
       </c>
       <c r="V35">
-        <v>1</v>
-      </c>
-      <c r="W35">
-        <v>350000</v>
+        <v>0</v>
+      </c>
+      <c r="W35" t="s">
+        <v>49</v>
       </c>
       <c r="X35" t="s">
-        <v>117</v>
+        <v>50</v>
       </c>
       <c r="Y35" t="s">
         <v>51</v>
@@ -8136,16 +8028,16 @@
         <v>55</v>
       </c>
       <c r="AD35" t="s">
-        <v>265</v>
+        <v>175</v>
       </c>
       <c r="AE35" t="s">
         <v>57</v>
       </c>
       <c r="AF35">
-        <v>100000000</v>
+        <v>325000000</v>
       </c>
       <c r="AG35">
-        <v>100000000</v>
+        <v>325000000</v>
       </c>
       <c r="AH35" t="s">
         <v>58</v>
@@ -8154,25 +8046,25 @@
         <v>49</v>
       </c>
       <c r="AJ35" t="s">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="AK35" t="s">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="AL35" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>2235</v>
+        <v>1661</v>
       </c>
       <c r="AM35" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>6.1232876712328768</v>
+        <v>4.5506849315068489</v>
       </c>
       <c r="AN35" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>6y</v>
+        <v>5y</v>
       </c>
       <c r="AO35">
-        <v>82.543000000000006</v>
+        <v>97.882000000000005</v>
       </c>
       <c r="AP35">
         <v>1000</v>
@@ -8180,22 +8072,22 @@
     </row>
     <row r="36" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C36" t="s">
         <v>62</v>
       </c>
       <c r="D36" t="s">
+        <v>265</v>
+      </c>
+      <c r="E36" t="s">
+        <v>266</v>
+      </c>
+      <c r="F36" t="s">
         <v>267</v>
       </c>
-      <c r="E36" t="s">
+      <c r="G36" t="s">
         <v>268</v>
-      </c>
-      <c r="F36" t="s">
-        <v>173</v>
-      </c>
-      <c r="G36" t="s">
-        <v>174</v>
       </c>
       <c r="H36" t="s">
         <v>42</v>
@@ -8204,7 +8096,7 @@
         <v>43</v>
       </c>
       <c r="J36">
-        <v>11.5</v>
+        <v>2</v>
       </c>
       <c r="K36" t="s">
         <v>44</v>
@@ -8222,10 +8114,10 @@
         <v>44</v>
       </c>
       <c r="P36" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q36" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R36" t="s">
         <v>49</v>
@@ -8234,10 +8126,10 @@
         <v>1</v>
       </c>
       <c r="T36">
-        <v>-143.66753763761881</v>
+        <v>-20.245024463954131</v>
       </c>
       <c r="U36">
-        <v>12.362524000000001</v>
+        <v>14.089100999999999</v>
       </c>
       <c r="V36">
         <v>0</v>
@@ -8264,16 +8156,16 @@
         <v>55</v>
       </c>
       <c r="AD36" t="s">
-        <v>175</v>
+        <v>269</v>
       </c>
       <c r="AE36" t="s">
         <v>57</v>
       </c>
       <c r="AF36">
-        <v>325000000</v>
+        <v>123000000</v>
       </c>
       <c r="AG36">
-        <v>325000000</v>
+        <v>123000000</v>
       </c>
       <c r="AH36" t="s">
         <v>58</v>
@@ -8289,18 +8181,18 @@
       </c>
       <c r="AL36" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>1662</v>
+        <v>441</v>
       </c>
       <c r="AM36" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>4.5534246575342463</v>
+        <v>1.2082191780821918</v>
       </c>
       <c r="AN36" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>5y</v>
+        <v>1y</v>
       </c>
       <c r="AO36">
-        <v>97.882000000000005</v>
+        <v>87.28</v>
       </c>
       <c r="AP36">
         <v>1000</v>
@@ -8308,22 +8200,22 @@
     </row>
     <row r="37" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C37" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="D37" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E37" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F37" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G37" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H37" t="s">
         <v>42</v>
@@ -8332,7 +8224,7 @@
         <v>43</v>
       </c>
       <c r="J37">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K37" t="s">
         <v>44</v>
@@ -8350,10 +8242,10 @@
         <v>44</v>
       </c>
       <c r="P37" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R37" t="s">
         <v>49</v>
@@ -8362,10 +8254,10 @@
         <v>1</v>
       </c>
       <c r="T37">
-        <v>-20.245024463954131</v>
+        <v>-113.89818739523835</v>
       </c>
       <c r="U37">
-        <v>14.089100999999999</v>
+        <v>12.517089</v>
       </c>
       <c r="V37">
         <v>0</v>
@@ -8392,16 +8284,16 @@
         <v>55</v>
       </c>
       <c r="AD37" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AE37" t="s">
         <v>57</v>
       </c>
       <c r="AF37">
-        <v>123000000</v>
+        <v>400000000</v>
       </c>
       <c r="AG37">
-        <v>123000000</v>
+        <v>400000000</v>
       </c>
       <c r="AH37" t="s">
         <v>58</v>
@@ -8417,18 +8309,18 @@
       </c>
       <c r="AL37" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>442</v>
+        <v>861</v>
       </c>
       <c r="AM37" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>1.210958904109589</v>
+        <v>2.3589041095890413</v>
       </c>
       <c r="AN37" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>1y</v>
+        <v>2y</v>
       </c>
       <c r="AO37">
-        <v>87.28</v>
+        <v>95.234999999999999</v>
       </c>
       <c r="AP37">
         <v>1000</v>
@@ -8436,22 +8328,22 @@
     </row>
     <row r="38" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C38" t="s">
-        <v>37</v>
+        <v>277</v>
       </c>
       <c r="D38" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E38" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F38" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G38" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H38" t="s">
         <v>42</v>
@@ -8460,7 +8352,7 @@
         <v>43</v>
       </c>
       <c r="J38">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="K38" t="s">
         <v>44</v>
@@ -8490,10 +8382,10 @@
         <v>1</v>
       </c>
       <c r="T38">
-        <v>-113.89818739523835</v>
+        <v>-159.2380271646972</v>
       </c>
       <c r="U38">
-        <v>12.517089</v>
+        <v>12.381271</v>
       </c>
       <c r="V38">
         <v>0</v>
@@ -8502,7 +8394,7 @@
         <v>49</v>
       </c>
       <c r="X38" t="s">
-        <v>50</v>
+        <v>282</v>
       </c>
       <c r="Y38" t="s">
         <v>51</v>
@@ -8520,16 +8412,16 @@
         <v>55</v>
       </c>
       <c r="AD38" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AE38" t="s">
         <v>57</v>
       </c>
       <c r="AF38">
-        <v>400000000</v>
+        <v>200000000</v>
       </c>
       <c r="AG38">
-        <v>400000000</v>
+        <v>200000000</v>
       </c>
       <c r="AH38" t="s">
         <v>58</v>
@@ -8541,22 +8433,22 @@
         <v>59</v>
       </c>
       <c r="AK38" t="s">
-        <v>60</v>
+        <v>284</v>
       </c>
       <c r="AL38" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>862</v>
+        <v>2073</v>
       </c>
       <c r="AM38" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>2.3616438356164382</v>
+        <v>5.6794520547945204</v>
       </c>
       <c r="AN38" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>2y</v>
+        <v>6y</v>
       </c>
       <c r="AO38">
-        <v>95.234999999999999</v>
+        <v>77.923000000000002</v>
       </c>
       <c r="AP38">
         <v>1000</v>
@@ -8564,22 +8456,22 @@
     </row>
     <row r="39" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C39" t="s">
-        <v>282</v>
+        <v>81</v>
       </c>
       <c r="D39" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E39" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F39" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="G39" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="H39" t="s">
         <v>42</v>
@@ -8588,7 +8480,7 @@
         <v>43</v>
       </c>
       <c r="J39">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="K39" t="s">
         <v>44</v>
@@ -8606,31 +8498,31 @@
         <v>44</v>
       </c>
       <c r="P39" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>49</v>
+      </c>
+      <c r="R39" t="s">
         <v>47</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>48</v>
-      </c>
-      <c r="R39" t="s">
-        <v>49</v>
       </c>
       <c r="S39">
         <v>1</v>
       </c>
       <c r="T39">
-        <v>-159.2380271646972</v>
+        <v>-145.60966255712432</v>
       </c>
       <c r="U39">
-        <v>12.381271</v>
-      </c>
-      <c r="V39">
-        <v>0</v>
+        <v>12.338996</v>
+      </c>
+      <c r="V39" t="s">
+        <v>49</v>
       </c>
       <c r="W39" t="s">
         <v>49</v>
       </c>
       <c r="X39" t="s">
-        <v>287</v>
+        <v>87</v>
       </c>
       <c r="Y39" t="s">
         <v>51</v>
@@ -8648,16 +8540,16 @@
         <v>55</v>
       </c>
       <c r="AD39" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AE39" t="s">
         <v>57</v>
       </c>
       <c r="AF39">
-        <v>200000000</v>
+        <v>600000000</v>
       </c>
       <c r="AG39">
-        <v>200000000</v>
+        <v>600000000</v>
       </c>
       <c r="AH39" t="s">
         <v>58</v>
@@ -8666,25 +8558,25 @@
         <v>49</v>
       </c>
       <c r="AJ39" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="AK39" t="s">
-        <v>289</v>
+        <v>89</v>
       </c>
       <c r="AL39" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>2074</v>
+        <v>1653</v>
       </c>
       <c r="AM39" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>5.6821917808219178</v>
+        <v>4.5287671232876709</v>
       </c>
       <c r="AN39" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>6y</v>
+        <v>5y</v>
       </c>
       <c r="AO39">
-        <v>77.923000000000002</v>
+        <v>86.162000000000006</v>
       </c>
       <c r="AP39">
         <v>1000</v>
@@ -8692,31 +8584,31 @@
     </row>
     <row r="40" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C40" t="s">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="D40" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E40" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F40" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G40" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H40" t="s">
         <v>42</v>
       </c>
       <c r="I40" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="J40">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K40" t="s">
         <v>44</v>
@@ -8737,19 +8629,19 @@
         <v>49</v>
       </c>
       <c r="Q40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R40" t="s">
-        <v>47</v>
-      </c>
-      <c r="S40">
-        <v>1</v>
+        <v>49</v>
+      </c>
+      <c r="S40" t="s">
+        <v>44</v>
       </c>
       <c r="T40">
-        <v>-145.60966255712432</v>
+        <v>-14.190160233351001</v>
       </c>
       <c r="U40">
-        <v>12.338996</v>
+        <v>14.295108000000001</v>
       </c>
       <c r="V40" t="s">
         <v>49</v>
@@ -8758,7 +8650,7 @@
         <v>49</v>
       </c>
       <c r="X40" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="Y40" t="s">
         <v>51</v>
@@ -8776,16 +8668,16 @@
         <v>55</v>
       </c>
       <c r="AD40" t="s">
-        <v>295</v>
+        <v>44</v>
       </c>
       <c r="AE40" t="s">
         <v>57</v>
       </c>
       <c r="AF40">
-        <v>600000000</v>
+        <v>70000000</v>
       </c>
       <c r="AG40">
-        <v>600000000</v>
+        <v>70000000</v>
       </c>
       <c r="AH40" t="s">
         <v>58</v>
@@ -8794,25 +8686,25 @@
         <v>49</v>
       </c>
       <c r="AJ40" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="AK40" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="AL40" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>1654</v>
+        <v>366</v>
       </c>
       <c r="AM40" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>4.5315068493150683</v>
+        <v>1.0027397260273974</v>
       </c>
       <c r="AN40" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>5y</v>
+        <v>1y</v>
       </c>
       <c r="AO40">
-        <v>86.162000000000006</v>
+        <v>87.322000000000003</v>
       </c>
       <c r="AP40">
         <v>1000</v>
@@ -8841,10 +8733,10 @@
         <v>42</v>
       </c>
       <c r="I41" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="K41" t="s">
         <v>44</v>
@@ -8862,7 +8754,7 @@
         <v>44</v>
       </c>
       <c r="P41" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q41" t="s">
         <v>48</v>
@@ -8870,17 +8762,17 @@
       <c r="R41" t="s">
         <v>49</v>
       </c>
-      <c r="S41" t="s">
-        <v>44</v>
+      <c r="S41">
+        <v>1</v>
       </c>
       <c r="T41">
-        <v>-14.190160233351001</v>
+        <v>-110.27430910451947</v>
       </c>
       <c r="U41">
-        <v>14.295108000000001</v>
-      </c>
-      <c r="V41" t="s">
-        <v>49</v>
+        <v>13.510757</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
       </c>
       <c r="W41" t="s">
         <v>49</v>
@@ -8904,16 +8796,16 @@
         <v>55</v>
       </c>
       <c r="AD41" t="s">
-        <v>44</v>
+        <v>301</v>
       </c>
       <c r="AE41" t="s">
         <v>57</v>
       </c>
       <c r="AF41">
-        <v>70000000</v>
+        <v>200000000</v>
       </c>
       <c r="AG41">
-        <v>70000000</v>
+        <v>200000000</v>
       </c>
       <c r="AH41" t="s">
         <v>58</v>
@@ -8929,18 +8821,18 @@
       </c>
       <c r="AL41" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>367</v>
+        <v>204</v>
       </c>
       <c r="AM41" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>1.0054794520547945</v>
+        <v>0.55890410958904113</v>
       </c>
       <c r="AN41" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>1y</v>
       </c>
       <c r="AO41">
-        <v>87.322000000000003</v>
+        <v>97.518000000000001</v>
       </c>
       <c r="AP41">
         <v>1000</v>
@@ -8948,22 +8840,22 @@
     </row>
     <row r="42" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C42" t="s">
-        <v>37</v>
+        <v>303</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E42" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F42" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G42" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="H42" t="s">
         <v>42</v>
@@ -8972,7 +8864,7 @@
         <v>43</v>
       </c>
       <c r="J42">
-        <v>9.5</v>
+        <v>11.4</v>
       </c>
       <c r="K42" t="s">
         <v>44</v>
@@ -8990,31 +8882,31 @@
         <v>44</v>
       </c>
       <c r="P42" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>49</v>
+      </c>
+      <c r="R42" t="s">
         <v>47</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>48</v>
-      </c>
-      <c r="R42" t="s">
-        <v>49</v>
       </c>
       <c r="S42">
         <v>1</v>
       </c>
       <c r="T42">
-        <v>-110.27430910451947</v>
+        <v>-130.40714671094094</v>
       </c>
       <c r="U42">
-        <v>13.510757</v>
-      </c>
-      <c r="V42">
-        <v>0</v>
+        <v>12.442792000000001</v>
+      </c>
+      <c r="V42" t="s">
+        <v>49</v>
       </c>
       <c r="W42" t="s">
         <v>49</v>
       </c>
       <c r="X42" t="s">
-        <v>50</v>
+        <v>282</v>
       </c>
       <c r="Y42" t="s">
         <v>51</v>
@@ -9032,16 +8924,16 @@
         <v>55</v>
       </c>
       <c r="AD42" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AE42" t="s">
         <v>57</v>
       </c>
       <c r="AF42">
-        <v>200000000</v>
+        <v>50000000</v>
       </c>
       <c r="AG42">
-        <v>200000000</v>
+        <v>50000000</v>
       </c>
       <c r="AH42" t="s">
         <v>58</v>
@@ -9053,22 +8945,22 @@
         <v>59</v>
       </c>
       <c r="AK42" t="s">
-        <v>60</v>
+        <v>284</v>
       </c>
       <c r="AL42" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>205</v>
+        <v>1455</v>
       </c>
       <c r="AM42" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.56164383561643838</v>
+        <v>3.9863013698630136</v>
       </c>
       <c r="AN42" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>1y</v>
+        <v>4y</v>
       </c>
       <c r="AO42">
-        <v>97.518000000000001</v>
+        <v>97.578999999999994</v>
       </c>
       <c r="AP42">
         <v>1000</v>
@@ -9076,31 +8968,31 @@
     </row>
     <row r="43" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C43" t="s">
-        <v>308</v>
+        <v>135</v>
       </c>
       <c r="D43" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E43" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F43" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G43" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H43" t="s">
         <v>42</v>
       </c>
       <c r="I43" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="J43">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="K43" t="s">
         <v>44</v>
@@ -9118,22 +9010,22 @@
         <v>44</v>
       </c>
       <c r="P43" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q43" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R43" t="s">
         <v>47</v>
       </c>
-      <c r="S43">
-        <v>1</v>
+      <c r="S43" t="s">
+        <v>44</v>
       </c>
       <c r="T43">
-        <v>-130.40714671094094</v>
+        <v>-166.04397759398034</v>
       </c>
       <c r="U43">
-        <v>12.442792000000001</v>
+        <v>12.328806</v>
       </c>
       <c r="V43" t="s">
         <v>49</v>
@@ -9142,7 +9034,7 @@
         <v>49</v>
       </c>
       <c r="X43" t="s">
-        <v>287</v>
+        <v>140</v>
       </c>
       <c r="Y43" t="s">
         <v>51</v>
@@ -9160,16 +9052,16 @@
         <v>55</v>
       </c>
       <c r="AD43" t="s">
-        <v>313</v>
+        <v>44</v>
       </c>
       <c r="AE43" t="s">
         <v>57</v>
       </c>
       <c r="AF43">
-        <v>50000000</v>
+        <v>550000000</v>
       </c>
       <c r="AG43">
-        <v>50000000</v>
+        <v>550000000</v>
       </c>
       <c r="AH43" t="s">
         <v>58</v>
@@ -9178,25 +9070,25 @@
         <v>49</v>
       </c>
       <c r="AJ43" t="s">
-        <v>59</v>
+        <v>142</v>
       </c>
       <c r="AK43" t="s">
-        <v>289</v>
+        <v>143</v>
       </c>
       <c r="AL43" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>1456</v>
+        <v>3262</v>
       </c>
       <c r="AM43" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>3.989041095890411</v>
+        <v>8.9369863013698634</v>
       </c>
       <c r="AN43" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>4y</v>
+        <v>9y</v>
       </c>
       <c r="AO43">
-        <v>97.578999999999994</v>
+        <v>35.82</v>
       </c>
       <c r="AP43">
         <v>1000</v>
@@ -9207,7 +9099,7 @@
         <v>314</v>
       </c>
       <c r="C44" t="s">
-        <v>135</v>
+        <v>37</v>
       </c>
       <c r="D44" t="s">
         <v>315</v>
@@ -9225,10 +9117,10 @@
         <v>42</v>
       </c>
       <c r="I44" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="K44" t="s">
         <v>44</v>
@@ -9252,16 +9144,16 @@
         <v>48</v>
       </c>
       <c r="R44" t="s">
-        <v>47</v>
-      </c>
-      <c r="S44" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="S44">
+        <v>1</v>
       </c>
       <c r="T44">
-        <v>-166.04397759398034</v>
+        <v>-92.332024377855674</v>
       </c>
       <c r="U44">
-        <v>12.328806</v>
+        <v>13.69018</v>
       </c>
       <c r="V44" t="s">
         <v>49</v>
@@ -9270,7 +9162,7 @@
         <v>49</v>
       </c>
       <c r="X44" t="s">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="Y44" t="s">
         <v>51</v>
@@ -9288,16 +9180,16 @@
         <v>55</v>
       </c>
       <c r="AD44" t="s">
-        <v>44</v>
+        <v>319</v>
       </c>
       <c r="AE44" t="s">
         <v>57</v>
       </c>
       <c r="AF44">
-        <v>550000000</v>
+        <v>150000000</v>
       </c>
       <c r="AG44">
-        <v>550000000</v>
+        <v>16360000</v>
       </c>
       <c r="AH44" t="s">
         <v>58</v>
@@ -9306,25 +9198,25 @@
         <v>49</v>
       </c>
       <c r="AJ44" t="s">
-        <v>142</v>
+        <v>59</v>
       </c>
       <c r="AK44" t="s">
-        <v>143</v>
+        <v>60</v>
       </c>
       <c r="AL44" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>3263</v>
+        <v>197</v>
       </c>
       <c r="AM44" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>8.9397260273972599</v>
+        <v>0.53972602739726028</v>
       </c>
       <c r="AN44" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>9y</v>
+        <v>1y</v>
       </c>
       <c r="AO44">
-        <v>35.82</v>
+        <v>98.519000000000005</v>
       </c>
       <c r="AP44">
         <v>1000</v>
@@ -9332,22 +9224,22 @@
     </row>
     <row r="45" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C45" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="D45" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E45" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F45" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G45" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H45" t="s">
         <v>42</v>
@@ -9356,7 +9248,7 @@
         <v>43</v>
       </c>
       <c r="J45">
-        <v>11.5</v>
+        <v>0.5</v>
       </c>
       <c r="K45" t="s">
         <v>44</v>
@@ -9374,10 +9266,10 @@
         <v>44</v>
       </c>
       <c r="P45" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q45" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R45" t="s">
         <v>49</v>
@@ -9386,10 +9278,10 @@
         <v>1</v>
       </c>
       <c r="T45">
-        <v>-92.332024377855674</v>
+        <v>-62.495194285957822</v>
       </c>
       <c r="U45">
-        <v>13.69018</v>
+        <v>13.020956999999999</v>
       </c>
       <c r="V45" t="s">
         <v>49</v>
@@ -9416,16 +9308,16 @@
         <v>55</v>
       </c>
       <c r="AD45" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AE45" t="s">
         <v>57</v>
       </c>
       <c r="AF45">
-        <v>150000000</v>
+        <v>57000000</v>
       </c>
       <c r="AG45">
-        <v>16360000</v>
+        <v>57000000</v>
       </c>
       <c r="AH45" t="s">
         <v>58</v>
@@ -9441,18 +9333,18 @@
       </c>
       <c r="AL45" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>198</v>
+        <v>870</v>
       </c>
       <c r="AM45" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.54246575342465753</v>
+        <v>2.3835616438356166</v>
       </c>
       <c r="AN45" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>1y</v>
+        <v>2y</v>
       </c>
       <c r="AO45">
-        <v>98.519000000000005</v>
+        <v>75.546999999999997</v>
       </c>
       <c r="AP45">
         <v>1000</v>
@@ -9460,31 +9352,31 @@
     </row>
     <row r="46" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C46" t="s">
-        <v>62</v>
+        <v>135</v>
       </c>
       <c r="D46" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E46" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F46" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G46" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H46" t="s">
         <v>42</v>
       </c>
       <c r="I46" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="J46">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K46" t="s">
         <v>44</v>
@@ -9502,22 +9394,22 @@
         <v>44</v>
       </c>
       <c r="P46" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R46" t="s">
-        <v>49</v>
-      </c>
-      <c r="S46">
-        <v>1</v>
+        <v>47</v>
+      </c>
+      <c r="S46" t="s">
+        <v>44</v>
       </c>
       <c r="T46">
-        <v>-62.495194285957822</v>
+        <v>-112.39571754161889</v>
       </c>
       <c r="U46">
-        <v>13.020956999999999</v>
+        <v>12.771227</v>
       </c>
       <c r="V46" t="s">
         <v>49</v>
@@ -9526,7 +9418,7 @@
         <v>49</v>
       </c>
       <c r="X46" t="s">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="Y46" t="s">
         <v>51</v>
@@ -9538,22 +9430,22 @@
         <v>53</v>
       </c>
       <c r="AB46" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="AC46" t="s">
         <v>55</v>
       </c>
       <c r="AD46" t="s">
-        <v>330</v>
+        <v>44</v>
       </c>
       <c r="AE46" t="s">
         <v>57</v>
       </c>
       <c r="AF46">
-        <v>57000000</v>
+        <v>330000000</v>
       </c>
       <c r="AG46">
-        <v>57000000</v>
+        <v>330000000</v>
       </c>
       <c r="AH46" t="s">
         <v>58</v>
@@ -9562,25 +9454,25 @@
         <v>49</v>
       </c>
       <c r="AJ46" t="s">
-        <v>59</v>
+        <v>142</v>
       </c>
       <c r="AK46" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="AL46" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>871</v>
+        <v>1848</v>
       </c>
       <c r="AM46" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>2.3863013698630136</v>
+        <v>5.0630136986301366</v>
       </c>
       <c r="AN46" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>2y</v>
+        <v>5y</v>
       </c>
       <c r="AO46">
-        <v>75.546999999999997</v>
+        <v>55.167000000000002</v>
       </c>
       <c r="AP46">
         <v>1000</v>
@@ -9591,7 +9483,7 @@
         <v>331</v>
       </c>
       <c r="C47" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="D47" t="s">
         <v>332</v>
@@ -9609,10 +9501,10 @@
         <v>42</v>
       </c>
       <c r="I47" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="K47" t="s">
         <v>44</v>
@@ -9630,22 +9522,22 @@
         <v>44</v>
       </c>
       <c r="P47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q47" t="s">
         <v>48</v>
       </c>
       <c r="R47" t="s">
-        <v>47</v>
-      </c>
-      <c r="S47" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="S47">
+        <v>1</v>
       </c>
       <c r="T47">
-        <v>-112.39571754161889</v>
+        <v>-111.14538221997225</v>
       </c>
       <c r="U47">
-        <v>12.771227</v>
+        <v>13.502046</v>
       </c>
       <c r="V47" t="s">
         <v>49</v>
@@ -9654,7 +9546,7 @@
         <v>49</v>
       </c>
       <c r="X47" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="Y47" t="s">
         <v>51</v>
@@ -9666,22 +9558,22 @@
         <v>53</v>
       </c>
       <c r="AB47" t="s">
-        <v>141</v>
+        <v>54</v>
       </c>
       <c r="AC47" t="s">
         <v>55</v>
       </c>
       <c r="AD47" t="s">
-        <v>44</v>
+        <v>336</v>
       </c>
       <c r="AE47" t="s">
         <v>57</v>
       </c>
       <c r="AF47">
-        <v>330000000</v>
+        <v>110000000</v>
       </c>
       <c r="AG47">
-        <v>330000000</v>
+        <v>110000000</v>
       </c>
       <c r="AH47" t="s">
         <v>58</v>
@@ -9690,25 +9582,25 @@
         <v>49</v>
       </c>
       <c r="AJ47" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="AK47" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="AL47" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>1849</v>
+        <v>273</v>
       </c>
       <c r="AM47" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>5.065753424657534</v>
+        <v>0.74794520547945209</v>
       </c>
       <c r="AN47" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>5y</v>
+        <v>1y</v>
       </c>
       <c r="AO47">
-        <v>55.167000000000002</v>
+        <v>97.597999999999999</v>
       </c>
       <c r="AP47">
         <v>1000</v>
@@ -9716,31 +9608,31 @@
     </row>
     <row r="48" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C48" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="D48" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E48" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F48" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G48" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H48" t="s">
         <v>42</v>
       </c>
       <c r="I48" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="J48">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="K48" t="s">
         <v>44</v>
@@ -9758,31 +9650,31 @@
         <v>44</v>
       </c>
       <c r="P48" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q48" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R48" t="s">
-        <v>49</v>
-      </c>
-      <c r="S48">
-        <v>1</v>
+        <v>47</v>
+      </c>
+      <c r="S48" t="s">
+        <v>44</v>
       </c>
       <c r="T48">
-        <v>-111.14538221997225</v>
+        <v>-110.62862080464804</v>
       </c>
       <c r="U48">
-        <v>13.502046</v>
-      </c>
-      <c r="V48" t="s">
-        <v>49</v>
+        <v>12.508848</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
       </c>
       <c r="W48" t="s">
         <v>49</v>
       </c>
       <c r="X48" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="Y48" t="s">
         <v>51</v>
@@ -9800,16 +9692,16 @@
         <v>55</v>
       </c>
       <c r="AD48" t="s">
-        <v>341</v>
+        <v>44</v>
       </c>
       <c r="AE48" t="s">
         <v>57</v>
       </c>
       <c r="AF48">
-        <v>110000000</v>
+        <v>100000000</v>
       </c>
       <c r="AG48">
-        <v>110000000</v>
+        <v>100000000</v>
       </c>
       <c r="AH48" t="s">
         <v>58</v>
@@ -9818,25 +9710,25 @@
         <v>49</v>
       </c>
       <c r="AJ48" t="s">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="AK48" t="s">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="AL48" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>274</v>
+        <v>981</v>
       </c>
       <c r="AM48" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75068493150684934</v>
+        <v>2.6876712328767125</v>
       </c>
       <c r="AN48" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>1y</v>
+        <v>3y</v>
       </c>
       <c r="AO48">
-        <v>97.597999999999999</v>
+        <v>73.364999999999995</v>
       </c>
       <c r="AP48">
         <v>1000</v>
@@ -9847,7 +9739,7 @@
         <v>342</v>
       </c>
       <c r="C49" t="s">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="D49" t="s">
         <v>343</v>
@@ -9886,22 +9778,22 @@
         <v>44</v>
       </c>
       <c r="P49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q49" t="s">
         <v>49</v>
       </c>
       <c r="R49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S49" t="s">
         <v>44</v>
       </c>
       <c r="T49">
-        <v>-110.62862080464804</v>
+        <v>-82.618448756819163</v>
       </c>
       <c r="U49">
-        <v>12.508848</v>
+        <v>13.775679</v>
       </c>
       <c r="V49">
         <v>0</v>
@@ -9910,7 +9802,7 @@
         <v>49</v>
       </c>
       <c r="X49" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="Y49" t="s">
         <v>51</v>
@@ -9922,7 +9814,7 @@
         <v>53</v>
       </c>
       <c r="AB49" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="AC49" t="s">
         <v>55</v>
@@ -9934,10 +9826,10 @@
         <v>57</v>
       </c>
       <c r="AF49">
-        <v>100000000</v>
+        <v>80000000</v>
       </c>
       <c r="AG49">
-        <v>100000000</v>
+        <v>80000000</v>
       </c>
       <c r="AH49" t="s">
         <v>58</v>
@@ -9946,25 +9838,25 @@
         <v>49</v>
       </c>
       <c r="AJ49" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="AK49" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="AL49" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>982</v>
+        <v>281</v>
       </c>
       <c r="AM49" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>2.6904109589041094</v>
+        <v>0.76986301369863008</v>
       </c>
       <c r="AN49" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>3y</v>
+        <v>1y</v>
       </c>
       <c r="AO49">
-        <v>73.364999999999995</v>
+        <v>90.355000000000004</v>
       </c>
       <c r="AP49">
         <v>1000</v>
@@ -9975,7 +9867,7 @@
         <v>347</v>
       </c>
       <c r="C50" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="D50" t="s">
         <v>348</v>
@@ -10026,13 +9918,13 @@
         <v>44</v>
       </c>
       <c r="T50">
-        <v>-82.618448756819163</v>
+        <v>-121.54262157755227</v>
       </c>
       <c r="U50">
-        <v>13.775679</v>
-      </c>
-      <c r="V50">
-        <v>0</v>
+        <v>12.698236</v>
+      </c>
+      <c r="V50" t="s">
+        <v>49</v>
       </c>
       <c r="W50" t="s">
         <v>49</v>
@@ -10050,7 +9942,7 @@
         <v>53</v>
       </c>
       <c r="AB50" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="AC50" t="s">
         <v>55</v>
@@ -10062,10 +9954,10 @@
         <v>57</v>
       </c>
       <c r="AF50">
-        <v>80000000</v>
+        <v>530000000</v>
       </c>
       <c r="AG50">
-        <v>80000000</v>
+        <v>530000000</v>
       </c>
       <c r="AH50" t="s">
         <v>58</v>
@@ -10081,18 +9973,18 @@
       </c>
       <c r="AL50" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>282</v>
+        <v>1884</v>
       </c>
       <c r="AM50" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77260273972602744</v>
+        <v>5.161643835616438</v>
       </c>
       <c r="AN50" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>1y</v>
+        <v>5y</v>
       </c>
       <c r="AO50">
-        <v>90.355000000000004</v>
+        <v>54.987000000000002</v>
       </c>
       <c r="AP50">
         <v>1000</v>
@@ -10103,7 +9995,7 @@
         <v>352</v>
       </c>
       <c r="C51" t="s">
-        <v>62</v>
+        <v>277</v>
       </c>
       <c r="D51" t="s">
         <v>353</v>
@@ -10112,19 +10004,19 @@
         <v>354</v>
       </c>
       <c r="F51" t="s">
-        <v>355</v>
+        <v>258</v>
       </c>
       <c r="G51" t="s">
-        <v>356</v>
+        <v>259</v>
       </c>
       <c r="H51" t="s">
         <v>42</v>
       </c>
       <c r="I51" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="K51" t="s">
         <v>44</v>
@@ -10150,14 +10042,14 @@
       <c r="R51" t="s">
         <v>49</v>
       </c>
-      <c r="S51" t="s">
-        <v>44</v>
+      <c r="S51">
+        <v>1</v>
       </c>
       <c r="T51">
-        <v>-121.54262157755227</v>
+        <v>-90.434904510439651</v>
       </c>
       <c r="U51">
-        <v>12.698236</v>
+        <v>13.055801000000001</v>
       </c>
       <c r="V51" t="s">
         <v>49</v>
@@ -10166,7 +10058,7 @@
         <v>49</v>
       </c>
       <c r="X51" t="s">
-        <v>50</v>
+        <v>282</v>
       </c>
       <c r="Y51" t="s">
         <v>51</v>
@@ -10178,22 +10070,22 @@
         <v>53</v>
       </c>
       <c r="AB51" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="AC51" t="s">
         <v>55</v>
       </c>
       <c r="AD51" t="s">
-        <v>44</v>
+        <v>260</v>
       </c>
       <c r="AE51" t="s">
         <v>57</v>
       </c>
       <c r="AF51">
-        <v>530000000</v>
+        <v>35770000</v>
       </c>
       <c r="AG51">
-        <v>530000000</v>
+        <v>35770000</v>
       </c>
       <c r="AH51" t="s">
         <v>58</v>
@@ -10205,22 +10097,22 @@
         <v>59</v>
       </c>
       <c r="AK51" t="s">
-        <v>60</v>
+        <v>284</v>
       </c>
       <c r="AL51" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>1885</v>
+        <v>2234</v>
       </c>
       <c r="AM51" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>5.1643835616438354</v>
+        <v>6.1205479452054794</v>
       </c>
       <c r="AN51" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>5y</v>
+        <v>6y</v>
       </c>
       <c r="AO51">
-        <v>54.987000000000002</v>
+        <v>81.403999999999996</v>
       </c>
       <c r="AP51">
         <v>1000</v>
@@ -10228,31 +10120,31 @@
     </row>
     <row r="52" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
+        <v>355</v>
+      </c>
+      <c r="C52" t="s">
+        <v>135</v>
+      </c>
+      <c r="D52" t="s">
+        <v>356</v>
+      </c>
+      <c r="E52" t="s">
         <v>357</v>
       </c>
-      <c r="C52" t="s">
-        <v>282</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="F52" t="s">
         <v>358</v>
       </c>
-      <c r="E52" t="s">
+      <c r="G52" t="s">
         <v>359</v>
-      </c>
-      <c r="F52" t="s">
-        <v>263</v>
-      </c>
-      <c r="G52" t="s">
-        <v>264</v>
       </c>
       <c r="H52" t="s">
         <v>42</v>
       </c>
       <c r="I52" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="J52">
-        <v>8.3000000000000007</v>
+        <v>0</v>
       </c>
       <c r="K52" t="s">
         <v>44</v>
@@ -10270,22 +10162,22 @@
         <v>44</v>
       </c>
       <c r="P52" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q52" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R52" t="s">
-        <v>49</v>
-      </c>
-      <c r="S52">
-        <v>1</v>
+        <v>47</v>
+      </c>
+      <c r="S52" t="s">
+        <v>44</v>
       </c>
       <c r="T52">
-        <v>-90.434904510439651</v>
+        <v>-93.344250466893726</v>
       </c>
       <c r="U52">
-        <v>13.055801000000001</v>
+        <v>13.680057</v>
       </c>
       <c r="V52" t="s">
         <v>49</v>
@@ -10294,7 +10186,7 @@
         <v>49</v>
       </c>
       <c r="X52" t="s">
-        <v>287</v>
+        <v>140</v>
       </c>
       <c r="Y52" t="s">
         <v>51</v>
@@ -10312,16 +10204,16 @@
         <v>55</v>
       </c>
       <c r="AD52" t="s">
-        <v>265</v>
+        <v>44</v>
       </c>
       <c r="AE52" t="s">
         <v>57</v>
       </c>
       <c r="AF52">
-        <v>35770000</v>
+        <v>200000000</v>
       </c>
       <c r="AG52">
-        <v>35770000</v>
+        <v>200000000</v>
       </c>
       <c r="AH52" t="s">
         <v>58</v>
@@ -10330,25 +10222,25 @@
         <v>49</v>
       </c>
       <c r="AJ52" t="s">
-        <v>59</v>
+        <v>142</v>
       </c>
       <c r="AK52" t="s">
-        <v>289</v>
+        <v>143</v>
       </c>
       <c r="AL52" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>2235</v>
+        <v>275</v>
       </c>
       <c r="AM52" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>6.1232876712328768</v>
+        <v>0.75342465753424659</v>
       </c>
       <c r="AN52" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>6y</v>
+        <v>1y</v>
       </c>
       <c r="AO52">
-        <v>81.403999999999996</v>
+        <v>90.566000000000003</v>
       </c>
       <c r="AP52">
         <v>1000</v>
@@ -10359,7 +10251,7 @@
         <v>360</v>
       </c>
       <c r="C53" t="s">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="D53" t="s">
         <v>361</v>
@@ -10377,10 +10269,10 @@
         <v>42</v>
       </c>
       <c r="I53" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="J53">
-        <v>0</v>
+        <v>8.27</v>
       </c>
       <c r="K53" t="s">
         <v>44</v>
@@ -10398,31 +10290,31 @@
         <v>44</v>
       </c>
       <c r="P53" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q53" t="s">
         <v>48</v>
       </c>
       <c r="R53" t="s">
-        <v>47</v>
-      </c>
-      <c r="S53" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="S53">
+        <v>1</v>
       </c>
       <c r="T53">
-        <v>-93.344250466893726</v>
+        <v>-104.26572917361358</v>
       </c>
       <c r="U53">
-        <v>13.680057</v>
-      </c>
-      <c r="V53" t="s">
-        <v>49</v>
+        <v>12.919924</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
       </c>
       <c r="W53" t="s">
         <v>49</v>
       </c>
       <c r="X53" t="s">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="Y53" t="s">
         <v>51</v>
@@ -10440,16 +10332,16 @@
         <v>55</v>
       </c>
       <c r="AD53" t="s">
-        <v>44</v>
+        <v>365</v>
       </c>
       <c r="AE53" t="s">
         <v>57</v>
       </c>
       <c r="AF53">
-        <v>200000000</v>
+        <v>55000000</v>
       </c>
       <c r="AG53">
-        <v>200000000</v>
+        <v>55000000</v>
       </c>
       <c r="AH53" t="s">
         <v>58</v>
@@ -10458,25 +10350,25 @@
         <v>49</v>
       </c>
       <c r="AJ53" t="s">
-        <v>142</v>
+        <v>59</v>
       </c>
       <c r="AK53" t="s">
-        <v>143</v>
+        <v>60</v>
       </c>
       <c r="AL53" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>276</v>
+        <v>2205</v>
       </c>
       <c r="AM53" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75616438356164384</v>
+        <v>6.0410958904109586</v>
       </c>
       <c r="AN53" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>1y</v>
+        <v>6y</v>
       </c>
       <c r="AO53">
-        <v>90.566000000000003</v>
+        <v>81.875</v>
       </c>
       <c r="AP53">
         <v>1000</v>
@@ -10484,22 +10376,22 @@
     </row>
     <row r="54" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C54" t="s">
-        <v>62</v>
+        <v>135</v>
       </c>
       <c r="D54" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E54" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F54" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G54" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H54" t="s">
         <v>42</v>
@@ -10508,7 +10400,7 @@
         <v>43</v>
       </c>
       <c r="J54">
-        <v>8.27</v>
+        <v>7.5</v>
       </c>
       <c r="K54" t="s">
         <v>44</v>
@@ -10526,31 +10418,31 @@
         <v>44</v>
       </c>
       <c r="P54" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q54" t="s">
         <v>48</v>
       </c>
       <c r="R54" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T54">
-        <v>-104.26572917361358</v>
+        <v>-137.13678648387173</v>
       </c>
       <c r="U54">
-        <v>12.919924</v>
-      </c>
-      <c r="V54">
-        <v>0</v>
+        <v>13.242132</v>
+      </c>
+      <c r="V54" t="s">
+        <v>49</v>
       </c>
       <c r="W54" t="s">
         <v>49</v>
       </c>
       <c r="X54" t="s">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="Y54" t="s">
         <v>51</v>
@@ -10568,16 +10460,16 @@
         <v>55</v>
       </c>
       <c r="AD54" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AE54" t="s">
         <v>57</v>
       </c>
       <c r="AF54">
-        <v>55000000</v>
+        <v>130000000</v>
       </c>
       <c r="AG54">
-        <v>55000000</v>
+        <v>130000000</v>
       </c>
       <c r="AH54" t="s">
         <v>58</v>
@@ -10586,25 +10478,25 @@
         <v>49</v>
       </c>
       <c r="AJ54" t="s">
-        <v>59</v>
+        <v>142</v>
       </c>
       <c r="AK54" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="AL54" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>2206</v>
+        <v>127</v>
       </c>
       <c r="AM54" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>6.043835616438356</v>
+        <v>0.34794520547945207</v>
       </c>
       <c r="AN54" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>6y</v>
+        <v>0y</v>
       </c>
       <c r="AO54">
-        <v>81.875</v>
+        <v>98.064999999999998</v>
       </c>
       <c r="AP54">
         <v>1000</v>
@@ -10612,22 +10504,22 @@
     </row>
     <row r="55" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C55" t="s">
-        <v>135</v>
+        <v>277</v>
       </c>
       <c r="D55" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E55" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F55" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G55" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H55" t="s">
         <v>42</v>
@@ -10636,7 +10528,7 @@
         <v>43</v>
       </c>
       <c r="J55">
-        <v>7.5</v>
+        <v>8.02</v>
       </c>
       <c r="K55" t="s">
         <v>44</v>
@@ -10654,22 +10546,22 @@
         <v>44</v>
       </c>
       <c r="P55" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q55" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R55" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T55">
-        <v>-137.13678648387173</v>
+        <v>-128.95226259222153</v>
       </c>
       <c r="U55">
-        <v>13.242132</v>
+        <v>12.678342000000001</v>
       </c>
       <c r="V55" t="s">
         <v>49</v>
@@ -10678,7 +10570,7 @@
         <v>49</v>
       </c>
       <c r="X55" t="s">
-        <v>140</v>
+        <v>282</v>
       </c>
       <c r="Y55" t="s">
         <v>51</v>
@@ -10696,16 +10588,16 @@
         <v>55</v>
       </c>
       <c r="AD55" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AE55" t="s">
         <v>57</v>
       </c>
       <c r="AF55">
-        <v>130000000</v>
+        <v>61310000</v>
       </c>
       <c r="AG55">
-        <v>130000000</v>
+        <v>61310000</v>
       </c>
       <c r="AH55" t="s">
         <v>58</v>
@@ -10714,25 +10606,25 @@
         <v>49</v>
       </c>
       <c r="AJ55" t="s">
-        <v>142</v>
+        <v>59</v>
       </c>
       <c r="AK55" t="s">
-        <v>143</v>
+        <v>284</v>
       </c>
       <c r="AL55" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>128</v>
+        <v>2142</v>
       </c>
       <c r="AM55" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.35068493150684932</v>
+        <v>5.8684931506849312</v>
       </c>
       <c r="AN55" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>0y</v>
+        <v>6y</v>
       </c>
       <c r="AO55">
-        <v>98.064999999999998</v>
+        <v>80.682000000000002</v>
       </c>
       <c r="AP55">
         <v>1000</v>
@@ -10740,31 +10632,31 @@
     </row>
     <row r="56" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C56" t="s">
-        <v>282</v>
+        <v>37</v>
       </c>
       <c r="D56" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E56" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F56" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G56" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H56" t="s">
         <v>42</v>
       </c>
       <c r="I56" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="J56">
-        <v>8.02</v>
+        <v>0</v>
       </c>
       <c r="K56" t="s">
         <v>44</v>
@@ -10790,14 +10682,14 @@
       <c r="R56" t="s">
         <v>49</v>
       </c>
-      <c r="S56">
-        <v>1</v>
+      <c r="S56" t="s">
+        <v>44</v>
       </c>
       <c r="T56">
-        <v>-128.95226259222153</v>
+        <v>-61.790560609508915</v>
       </c>
       <c r="U56">
-        <v>12.678342000000001</v>
+        <v>13.065263</v>
       </c>
       <c r="V56" t="s">
         <v>49</v>
@@ -10806,7 +10698,7 @@
         <v>49</v>
       </c>
       <c r="X56" t="s">
-        <v>287</v>
+        <v>50</v>
       </c>
       <c r="Y56" t="s">
         <v>51</v>
@@ -10824,16 +10716,16 @@
         <v>55</v>
       </c>
       <c r="AD56" t="s">
-        <v>382</v>
+        <v>44</v>
       </c>
       <c r="AE56" t="s">
         <v>57</v>
       </c>
       <c r="AF56">
-        <v>61310000</v>
+        <v>85000000</v>
       </c>
       <c r="AG56">
-        <v>61310000</v>
+        <v>85000000</v>
       </c>
       <c r="AH56" t="s">
         <v>58</v>
@@ -10845,22 +10737,22 @@
         <v>59</v>
       </c>
       <c r="AK56" t="s">
-        <v>289</v>
+        <v>60</v>
       </c>
       <c r="AL56" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>2143</v>
+        <v>837</v>
       </c>
       <c r="AM56" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>5.8712328767123285</v>
+        <v>2.2931506849315069</v>
       </c>
       <c r="AN56" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>6y</v>
+        <v>2y</v>
       </c>
       <c r="AO56">
-        <v>80.682000000000002</v>
+        <v>75.802000000000007</v>
       </c>
       <c r="AP56">
         <v>1000</v>
@@ -10871,7 +10763,7 @@
         <v>383</v>
       </c>
       <c r="C57" t="s">
-        <v>37</v>
+        <v>135</v>
       </c>
       <c r="D57" t="s">
         <v>384</v>
@@ -10880,10 +10772,10 @@
         <v>385</v>
       </c>
       <c r="F57" t="s">
-        <v>240</v>
+        <v>386</v>
       </c>
       <c r="G57" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H57" t="s">
         <v>42</v>
@@ -10892,7 +10784,7 @@
         <v>43</v>
       </c>
       <c r="J57">
-        <v>5.3049999999999997</v>
+        <v>8.86</v>
       </c>
       <c r="K57" t="s">
         <v>44</v>
@@ -10910,22 +10802,22 @@
         <v>44</v>
       </c>
       <c r="P57" t="s">
-        <v>387</v>
+        <v>47</v>
       </c>
       <c r="Q57" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="R57" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S57">
-        <v>1</v>
-      </c>
-      <c r="T57" t="s">
-        <v>49</v>
-      </c>
-      <c r="U57" t="s">
-        <v>49</v>
+        <v>2</v>
+      </c>
+      <c r="T57">
+        <v>-94.377194115754293</v>
+      </c>
+      <c r="U57">
+        <v>13.016795999999999</v>
       </c>
       <c r="V57" t="s">
         <v>49</v>
@@ -10934,7 +10826,7 @@
         <v>49</v>
       </c>
       <c r="X57" t="s">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="Y57" t="s">
         <v>51</v>
@@ -10946,7 +10838,7 @@
         <v>53</v>
       </c>
       <c r="AB57" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
       <c r="AC57" t="s">
         <v>55</v>
@@ -10958,10 +10850,10 @@
         <v>57</v>
       </c>
       <c r="AF57">
-        <v>53500000</v>
+        <v>60000000</v>
       </c>
       <c r="AG57">
-        <v>53500000</v>
+        <v>60000000</v>
       </c>
       <c r="AH57" t="s">
         <v>58</v>
@@ -10970,25 +10862,25 @@
         <v>49</v>
       </c>
       <c r="AJ57" t="s">
-        <v>59</v>
+        <v>142</v>
       </c>
       <c r="AK57" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="AL57" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>197</v>
+        <v>3054</v>
       </c>
       <c r="AM57" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.53972602739726028</v>
+        <v>8.367123287671232</v>
       </c>
       <c r="AN57" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>1y</v>
-      </c>
-      <c r="AO57" t="s">
-        <v>49</v>
+        <v>8y</v>
+      </c>
+      <c r="AO57">
+        <v>81.733999999999995</v>
       </c>
       <c r="AP57">
         <v>1000</v>
@@ -10996,22 +10888,22 @@
     </row>
     <row r="58" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="C58" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="D58" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="E58" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="F58" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="G58" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="H58" t="s">
         <v>42</v>
@@ -11038,10 +10930,10 @@
         <v>44</v>
       </c>
       <c r="P58" t="s">
-        <v>387</v>
+        <v>49</v>
       </c>
       <c r="Q58" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="R58" t="s">
         <v>49</v>
@@ -11049,11 +10941,11 @@
       <c r="S58" t="s">
         <v>44</v>
       </c>
-      <c r="T58" t="s">
-        <v>49</v>
-      </c>
-      <c r="U58" t="s">
-        <v>49</v>
+      <c r="T58">
+        <v>-17.23631939447845</v>
+      </c>
+      <c r="U58">
+        <v>13.463384</v>
       </c>
       <c r="V58" t="s">
         <v>49</v>
@@ -11086,10 +10978,10 @@
         <v>57</v>
       </c>
       <c r="AF58">
-        <v>168630000</v>
+        <v>40230000</v>
       </c>
       <c r="AG58">
-        <v>168630000</v>
+        <v>40230000</v>
       </c>
       <c r="AH58" t="s">
         <v>58</v>
@@ -11105,18 +10997,18 @@
       </c>
       <c r="AL58" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>134</v>
+        <v>879</v>
       </c>
       <c r="AM58" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.36712328767123287</v>
+        <v>2.408219178082192</v>
       </c>
       <c r="AN58" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>0y</v>
-      </c>
-      <c r="AO58" t="s">
-        <v>49</v>
+        <v>2y</v>
+      </c>
+      <c r="AO58">
+        <v>74.078000000000003</v>
       </c>
       <c r="AP58">
         <v>1000</v>
@@ -11124,22 +11016,22 @@
     </row>
     <row r="59" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="C59" t="s">
-        <v>389</v>
+        <v>62</v>
       </c>
       <c r="D59" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="E59" t="s">
-        <v>44</v>
+        <v>396</v>
       </c>
       <c r="F59" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="G59" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="H59" t="s">
         <v>42</v>
@@ -11177,20 +11069,20 @@
       <c r="S59" t="s">
         <v>44</v>
       </c>
-      <c r="T59" t="s">
-        <v>49</v>
-      </c>
-      <c r="U59" t="s">
-        <v>49</v>
-      </c>
-      <c r="V59" t="s">
-        <v>49</v>
-      </c>
-      <c r="W59" t="s">
-        <v>49</v>
+      <c r="T59">
+        <v>-92.860341236572097</v>
+      </c>
+      <c r="U59">
+        <v>13.684896999999999</v>
+      </c>
+      <c r="V59">
+        <v>3</v>
+      </c>
+      <c r="W59">
+        <v>880000</v>
       </c>
       <c r="X59" t="s">
-        <v>391</v>
+        <v>50</v>
       </c>
       <c r="Y59" t="s">
         <v>51</v>
@@ -11202,7 +11094,7 @@
         <v>53</v>
       </c>
       <c r="AB59" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="AC59" t="s">
         <v>55</v>
@@ -11214,37 +11106,37 @@
         <v>57</v>
       </c>
       <c r="AF59">
-        <v>80000000</v>
+        <v>180000000</v>
       </c>
       <c r="AG59">
-        <v>80000000</v>
+        <v>120100000</v>
       </c>
       <c r="AH59" t="s">
-        <v>392</v>
+        <v>58</v>
       </c>
       <c r="AI59" t="s">
         <v>49</v>
       </c>
       <c r="AJ59" t="s">
-        <v>393</v>
+        <v>59</v>
       </c>
       <c r="AK59" t="s">
-        <v>394</v>
+        <v>60</v>
       </c>
       <c r="AL59" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>343</v>
+        <v>86</v>
       </c>
       <c r="AM59" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9397260273972603</v>
+        <v>0.23561643835616439</v>
       </c>
       <c r="AN59" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>1y</v>
-      </c>
-      <c r="AO59" t="s">
-        <v>49</v>
+        <v>0y</v>
+      </c>
+      <c r="AO59">
+        <v>97.054000000000002</v>
       </c>
       <c r="AP59">
         <v>1000</v>
@@ -11252,31 +11144,31 @@
     </row>
     <row r="60" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
+        <v>399</v>
+      </c>
+      <c r="C60" t="s">
+        <v>135</v>
+      </c>
+      <c r="D60" t="s">
+        <v>400</v>
+      </c>
+      <c r="E60" t="s">
+        <v>401</v>
+      </c>
+      <c r="F60" t="s">
+        <v>402</v>
+      </c>
+      <c r="G60" t="s">
         <v>403</v>
-      </c>
-      <c r="C60" t="s">
-        <v>37</v>
-      </c>
-      <c r="D60" t="s">
-        <v>404</v>
-      </c>
-      <c r="E60" t="s">
-        <v>405</v>
-      </c>
-      <c r="F60" t="s">
-        <v>406</v>
-      </c>
-      <c r="G60" t="s">
-        <v>407</v>
       </c>
       <c r="H60" t="s">
         <v>42</v>
       </c>
       <c r="I60" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>9.7100000000000009</v>
       </c>
       <c r="K60" t="s">
         <v>44</v>
@@ -11294,22 +11186,22 @@
         <v>44</v>
       </c>
       <c r="P60" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q60" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R60" t="s">
-        <v>49</v>
-      </c>
-      <c r="S60" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+      <c r="S60">
+        <v>2</v>
       </c>
       <c r="T60">
-        <v>-61.790560609508915</v>
+        <v>-114.19046839371205</v>
       </c>
       <c r="U60">
-        <v>13.065263</v>
+        <v>13.281529000000001</v>
       </c>
       <c r="V60" t="s">
         <v>49</v>
@@ -11318,7 +11210,7 @@
         <v>49</v>
       </c>
       <c r="X60" t="s">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="Y60" t="s">
         <v>51</v>
@@ -11336,16 +11228,16 @@
         <v>55</v>
       </c>
       <c r="AD60" t="s">
-        <v>44</v>
+        <v>404</v>
       </c>
       <c r="AE60" t="s">
         <v>57</v>
       </c>
       <c r="AF60">
-        <v>85000000</v>
+        <v>6000000</v>
       </c>
       <c r="AG60">
-        <v>85000000</v>
+        <v>6000000</v>
       </c>
       <c r="AH60" t="s">
         <v>58</v>
@@ -11354,25 +11246,25 @@
         <v>49</v>
       </c>
       <c r="AJ60" t="s">
-        <v>59</v>
+        <v>142</v>
       </c>
       <c r="AK60" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="AL60" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>838</v>
+        <v>373</v>
       </c>
       <c r="AM60" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>2.2958904109589042</v>
+        <v>1.021917808219178</v>
       </c>
       <c r="AN60" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>2y</v>
+        <v>1y</v>
       </c>
       <c r="AO60">
-        <v>75.802000000000007</v>
+        <v>97.043999999999997</v>
       </c>
       <c r="AP60">
         <v>1000</v>
@@ -11380,22 +11272,22 @@
     </row>
     <row r="61" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
+        <v>405</v>
+      </c>
+      <c r="C61" t="s">
+        <v>37</v>
+      </c>
+      <c r="D61" t="s">
+        <v>406</v>
+      </c>
+      <c r="E61" t="s">
+        <v>407</v>
+      </c>
+      <c r="F61" t="s">
         <v>408</v>
       </c>
-      <c r="C61" t="s">
-        <v>135</v>
-      </c>
-      <c r="D61" t="s">
+      <c r="G61" t="s">
         <v>409</v>
-      </c>
-      <c r="E61" t="s">
-        <v>410</v>
-      </c>
-      <c r="F61" t="s">
-        <v>411</v>
-      </c>
-      <c r="G61" t="s">
-        <v>412</v>
       </c>
       <c r="H61" t="s">
         <v>42</v>
@@ -11404,7 +11296,7 @@
         <v>43</v>
       </c>
       <c r="J61">
-        <v>8.86</v>
+        <v>8</v>
       </c>
       <c r="K61" t="s">
         <v>44</v>
@@ -11422,22 +11314,22 @@
         <v>44</v>
       </c>
       <c r="P61" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q61" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R61" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S61">
         <v>2</v>
       </c>
       <c r="T61">
-        <v>-94.377194115754293</v>
+        <v>-30.739862007838248</v>
       </c>
       <c r="U61">
-        <v>13.016795999999999</v>
+        <v>13.359643</v>
       </c>
       <c r="V61" t="s">
         <v>49</v>
@@ -11446,7 +11338,7 @@
         <v>49</v>
       </c>
       <c r="X61" t="s">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="Y61" t="s">
         <v>51</v>
@@ -11458,22 +11350,22 @@
         <v>53</v>
       </c>
       <c r="AB61" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="AC61" t="s">
         <v>55</v>
       </c>
       <c r="AD61" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="AE61" t="s">
         <v>57</v>
       </c>
       <c r="AF61">
-        <v>60000000</v>
+        <v>19500000</v>
       </c>
       <c r="AG61">
-        <v>60000000</v>
+        <v>19500000</v>
       </c>
       <c r="AH61" t="s">
         <v>58</v>
@@ -11482,25 +11374,25 @@
         <v>49</v>
       </c>
       <c r="AJ61" t="s">
-        <v>142</v>
+        <v>59</v>
       </c>
       <c r="AK61" t="s">
-        <v>143</v>
+        <v>60</v>
       </c>
       <c r="AL61" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>3055</v>
+        <v>1152</v>
       </c>
       <c r="AM61" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>8.3698630136986303</v>
+        <v>3.1561643835616437</v>
       </c>
       <c r="AN61" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>8y</v>
+        <v>3y</v>
       </c>
       <c r="AO61">
-        <v>81.733999999999995</v>
+        <v>88.266999999999996</v>
       </c>
       <c r="AP61">
         <v>1000</v>
@@ -11508,31 +11400,31 @@
     </row>
     <row r="62" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
+        <v>411</v>
+      </c>
+      <c r="C62" t="s">
+        <v>277</v>
+      </c>
+      <c r="D62" t="s">
+        <v>412</v>
+      </c>
+      <c r="E62" t="s">
+        <v>413</v>
+      </c>
+      <c r="F62" t="s">
         <v>414</v>
       </c>
-      <c r="C62" t="s">
-        <v>62</v>
-      </c>
-      <c r="D62" t="s">
+      <c r="G62" t="s">
         <v>415</v>
-      </c>
-      <c r="E62" t="s">
-        <v>416</v>
-      </c>
-      <c r="F62" t="s">
-        <v>417</v>
-      </c>
-      <c r="G62" t="s">
-        <v>418</v>
       </c>
       <c r="H62" t="s">
         <v>42</v>
       </c>
       <c r="I62" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="J62">
-        <v>0</v>
+        <v>9.65</v>
       </c>
       <c r="K62" t="s">
         <v>44</v>
@@ -11553,19 +11445,19 @@
         <v>49</v>
       </c>
       <c r="Q62" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R62" t="s">
         <v>49</v>
       </c>
-      <c r="S62" t="s">
-        <v>44</v>
+      <c r="S62">
+        <v>1</v>
       </c>
       <c r="T62">
-        <v>-17.23631939447845</v>
+        <v>-105.66356298379293</v>
       </c>
       <c r="U62">
-        <v>13.463384</v>
+        <v>12.899488999999999</v>
       </c>
       <c r="V62" t="s">
         <v>49</v>
@@ -11574,7 +11466,7 @@
         <v>49</v>
       </c>
       <c r="X62" t="s">
-        <v>50</v>
+        <v>282</v>
       </c>
       <c r="Y62" t="s">
         <v>51</v>
@@ -11592,16 +11484,16 @@
         <v>55</v>
       </c>
       <c r="AD62" t="s">
-        <v>44</v>
+        <v>416</v>
       </c>
       <c r="AE62" t="s">
         <v>57</v>
       </c>
       <c r="AF62">
-        <v>40230000</v>
+        <v>58800000</v>
       </c>
       <c r="AG62">
-        <v>40230000</v>
+        <v>58800000</v>
       </c>
       <c r="AH62" t="s">
         <v>58</v>
@@ -11613,22 +11505,22 @@
         <v>59</v>
       </c>
       <c r="AK62" t="s">
-        <v>60</v>
+        <v>284</v>
       </c>
       <c r="AL62" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>880</v>
+        <f t="shared" ref="AL62:AL64" ca="1" si="3">G62-$AQ$2</f>
+        <v>2282</v>
       </c>
       <c r="AM62" s="3">
-        <f t="shared" ca="1" si="1"/>
-        <v>2.4109589041095889</v>
+        <f t="shared" ref="AM62:AM64" ca="1" si="4">AL62/365</f>
+        <v>6.2520547945205482</v>
       </c>
       <c r="AN62" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>2y</v>
+        <f t="shared" ref="AN62:AN64" ca="1" si="5">IF(AM62&gt;36,"&gt;36y",ROUND(AM62,0)&amp;"y")</f>
+        <v>6y</v>
       </c>
       <c r="AO62">
-        <v>74.078000000000003</v>
+        <v>87.180999999999997</v>
       </c>
       <c r="AP62">
         <v>1000</v>
@@ -11636,22 +11528,22 @@
     </row>
     <row r="63" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
+        <v>417</v>
+      </c>
+      <c r="C63" t="s">
+        <v>135</v>
+      </c>
+      <c r="D63" t="s">
+        <v>418</v>
+      </c>
+      <c r="E63" t="s">
         <v>419</v>
       </c>
-      <c r="C63" t="s">
-        <v>62</v>
-      </c>
-      <c r="D63" t="s">
+      <c r="F63" t="s">
         <v>420</v>
       </c>
-      <c r="E63" t="s">
+      <c r="G63" t="s">
         <v>421</v>
-      </c>
-      <c r="F63" t="s">
-        <v>422</v>
-      </c>
-      <c r="G63" t="s">
-        <v>423</v>
       </c>
       <c r="H63" t="s">
         <v>42</v>
@@ -11678,31 +11570,31 @@
         <v>44</v>
       </c>
       <c r="P63" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q63" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R63" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S63" t="s">
         <v>44</v>
       </c>
       <c r="T63">
-        <v>-92.860341236572097</v>
+        <v>-94.463254019144216</v>
       </c>
       <c r="U63">
-        <v>13.684896999999999</v>
-      </c>
-      <c r="V63">
-        <v>3</v>
-      </c>
-      <c r="W63">
-        <v>880000</v>
+        <v>12.723623</v>
+      </c>
+      <c r="V63" t="s">
+        <v>49</v>
+      </c>
+      <c r="W63" t="s">
+        <v>49</v>
       </c>
       <c r="X63" t="s">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="Y63" t="s">
         <v>51</v>
@@ -11714,7 +11606,7 @@
         <v>53</v>
       </c>
       <c r="AB63" t="s">
-        <v>141</v>
+        <v>54</v>
       </c>
       <c r="AC63" t="s">
         <v>55</v>
@@ -11726,10 +11618,10 @@
         <v>57</v>
       </c>
       <c r="AF63">
-        <v>180000000</v>
+        <v>72000000</v>
       </c>
       <c r="AG63">
-        <v>120100000</v>
+        <v>72000000</v>
       </c>
       <c r="AH63" t="s">
         <v>58</v>
@@ -11738,25 +11630,25 @@
         <v>49</v>
       </c>
       <c r="AJ63" t="s">
-        <v>59</v>
+        <v>142</v>
       </c>
       <c r="AK63" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="AL63" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>87</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>1156</v>
       </c>
       <c r="AM63" s="3">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.23835616438356164</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>3.1671232876712327</v>
       </c>
       <c r="AN63" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>0y</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>3y</v>
       </c>
       <c r="AO63">
-        <v>97.054000000000002</v>
+        <v>68.972999999999999</v>
       </c>
       <c r="AP63">
         <v>1000</v>
@@ -11764,22 +11656,22 @@
     </row>
     <row r="64" spans="2:42" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C64" t="s">
         <v>135</v>
       </c>
       <c r="D64" t="s">
+        <v>423</v>
+      </c>
+      <c r="E64" t="s">
+        <v>424</v>
+      </c>
+      <c r="F64" t="s">
         <v>425</v>
       </c>
-      <c r="E64" t="s">
+      <c r="G64" t="s">
         <v>426</v>
-      </c>
-      <c r="F64" t="s">
-        <v>427</v>
-      </c>
-      <c r="G64" t="s">
-        <v>428</v>
       </c>
       <c r="H64" t="s">
         <v>42</v>
@@ -11788,7 +11680,7 @@
         <v>43</v>
       </c>
       <c r="J64">
-        <v>9.7100000000000009</v>
+        <v>9.5</v>
       </c>
       <c r="K64" t="s">
         <v>44</v>
@@ -11818,10 +11710,10 @@
         <v>2</v>
       </c>
       <c r="T64">
-        <v>-114.19046839371205</v>
+        <v>-62.836857008190528</v>
       </c>
       <c r="U64">
-        <v>13.281529000000001</v>
+        <v>13.216260999999999</v>
       </c>
       <c r="V64" t="s">
         <v>49</v>
@@ -11848,7 +11740,7 @@
         <v>55</v>
       </c>
       <c r="AD64" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AE64" t="s">
         <v>57</v>
@@ -11872,794 +11764,26 @@
         <v>143</v>
       </c>
       <c r="AL64" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>374</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>694</v>
       </c>
       <c r="AM64" s="3">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.0246575342465754</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1.9013698630136986</v>
       </c>
       <c r="AN64" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>1y</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>2y</v>
       </c>
       <c r="AO64">
-        <v>97.043999999999997</v>
+        <v>94.644000000000005</v>
       </c>
       <c r="AP64">
         <v>1000</v>
       </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.25">
-      <c r="B65" t="s">
-        <v>430</v>
-      </c>
-      <c r="C65" t="s">
-        <v>37</v>
-      </c>
-      <c r="D65" t="s">
-        <v>431</v>
-      </c>
-      <c r="E65" t="s">
-        <v>432</v>
-      </c>
-      <c r="F65" t="s">
-        <v>433</v>
-      </c>
-      <c r="G65" t="s">
-        <v>434</v>
-      </c>
-      <c r="H65" t="s">
-        <v>42</v>
-      </c>
-      <c r="I65" t="s">
-        <v>43</v>
-      </c>
-      <c r="J65">
-        <v>8</v>
-      </c>
-      <c r="K65" t="s">
-        <v>44</v>
-      </c>
-      <c r="L65" t="s">
-        <v>45</v>
-      </c>
-      <c r="M65">
-        <v>1</v>
-      </c>
-      <c r="N65" t="s">
-        <v>46</v>
-      </c>
-      <c r="O65" t="s">
-        <v>44</v>
-      </c>
-      <c r="P65" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q65" t="s">
-        <v>49</v>
-      </c>
-      <c r="R65" t="s">
-        <v>49</v>
-      </c>
-      <c r="S65">
-        <v>2</v>
-      </c>
-      <c r="T65">
-        <v>-30.739862007838248</v>
-      </c>
-      <c r="U65">
-        <v>13.359643</v>
-      </c>
-      <c r="V65" t="s">
-        <v>49</v>
-      </c>
-      <c r="W65" t="s">
-        <v>49</v>
-      </c>
-      <c r="X65" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y65" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z65" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA65" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB65" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC65" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD65" t="s">
-        <v>435</v>
-      </c>
-      <c r="AE65" t="s">
-        <v>57</v>
-      </c>
-      <c r="AF65">
-        <v>19500000</v>
-      </c>
-      <c r="AG65">
-        <v>19500000</v>
-      </c>
-      <c r="AH65" t="s">
-        <v>58</v>
-      </c>
-      <c r="AI65" t="s">
-        <v>49</v>
-      </c>
-      <c r="AJ65" t="s">
-        <v>59</v>
-      </c>
-      <c r="AK65" t="s">
-        <v>60</v>
-      </c>
-      <c r="AL65" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>1153</v>
-      </c>
-      <c r="AM65" s="3">
-        <f t="shared" ca="1" si="1"/>
-        <v>3.1589041095890411</v>
-      </c>
-      <c r="AN65" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>3y</v>
-      </c>
-      <c r="AO65">
-        <v>88.266999999999996</v>
-      </c>
-      <c r="AP65">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.25">
-      <c r="B66" t="s">
-        <v>436</v>
-      </c>
-      <c r="C66" t="s">
-        <v>37</v>
-      </c>
-      <c r="D66" t="s">
-        <v>437</v>
-      </c>
-      <c r="E66" t="s">
-        <v>438</v>
-      </c>
-      <c r="F66" t="s">
-        <v>439</v>
-      </c>
-      <c r="G66" t="s">
-        <v>440</v>
-      </c>
-      <c r="H66" t="s">
-        <v>42</v>
-      </c>
-      <c r="I66" t="s">
-        <v>43</v>
-      </c>
-      <c r="J66">
-        <v>8.1</v>
-      </c>
-      <c r="K66" t="s">
-        <v>44</v>
-      </c>
-      <c r="L66" t="s">
-        <v>45</v>
-      </c>
-      <c r="M66">
-        <v>1</v>
-      </c>
-      <c r="N66" t="s">
-        <v>46</v>
-      </c>
-      <c r="O66" t="s">
-        <v>44</v>
-      </c>
-      <c r="P66" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q66" t="s">
-        <v>49</v>
-      </c>
-      <c r="R66" t="s">
-        <v>49</v>
-      </c>
-      <c r="S66">
-        <v>2</v>
-      </c>
-      <c r="T66">
-        <v>-253.67807448283716</v>
-      </c>
-      <c r="U66">
-        <v>12.076719000000001</v>
-      </c>
-      <c r="V66" t="s">
-        <v>49</v>
-      </c>
-      <c r="W66" t="s">
-        <v>49</v>
-      </c>
-      <c r="X66" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y66" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z66" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA66" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB66" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC66" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD66" t="s">
-        <v>441</v>
-      </c>
-      <c r="AE66" t="s">
-        <v>57</v>
-      </c>
-      <c r="AF66">
-        <v>12000000</v>
-      </c>
-      <c r="AG66">
-        <v>12000000</v>
-      </c>
-      <c r="AH66" t="s">
-        <v>58</v>
-      </c>
-      <c r="AI66" t="s">
-        <v>49</v>
-      </c>
-      <c r="AJ66" t="s">
-        <v>59</v>
-      </c>
-      <c r="AK66" t="s">
-        <v>60</v>
-      </c>
-      <c r="AL66" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>-4</v>
-      </c>
-      <c r="AM66" s="3">
-        <f t="shared" ca="1" si="1"/>
-        <v>-1.0958904109589041E-2</v>
-      </c>
-      <c r="AN66" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>0y</v>
-      </c>
-      <c r="AO66" t="s">
-        <v>49</v>
-      </c>
-      <c r="AP66">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.25">
-      <c r="B67" t="s">
-        <v>442</v>
-      </c>
-      <c r="C67" t="s">
-        <v>389</v>
-      </c>
-      <c r="D67" t="s">
-        <v>443</v>
-      </c>
-      <c r="E67" t="s">
-        <v>444</v>
-      </c>
-      <c r="F67" t="s">
-        <v>445</v>
-      </c>
-      <c r="G67" t="s">
-        <v>446</v>
-      </c>
-      <c r="H67" t="s">
-        <v>42</v>
-      </c>
-      <c r="I67" t="s">
-        <v>79</v>
-      </c>
-      <c r="J67">
-        <v>0</v>
-      </c>
-      <c r="K67" t="s">
-        <v>44</v>
-      </c>
-      <c r="L67" t="s">
-        <v>45</v>
-      </c>
-      <c r="M67">
-        <v>1</v>
-      </c>
-      <c r="N67" t="s">
-        <v>46</v>
-      </c>
-      <c r="O67" t="s">
-        <v>44</v>
-      </c>
-      <c r="P67" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q67" t="s">
-        <v>49</v>
-      </c>
-      <c r="R67" t="s">
-        <v>49</v>
-      </c>
-      <c r="S67" t="s">
-        <v>44</v>
-      </c>
-      <c r="T67" t="s">
-        <v>49</v>
-      </c>
-      <c r="U67" t="s">
-        <v>49</v>
-      </c>
-      <c r="V67" t="s">
-        <v>49</v>
-      </c>
-      <c r="W67" t="s">
-        <v>49</v>
-      </c>
-      <c r="X67" t="s">
-        <v>391</v>
-      </c>
-      <c r="Y67" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z67" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA67" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB67" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC67" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD67" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE67" t="s">
-        <v>57</v>
-      </c>
-      <c r="AF67">
-        <v>260750000</v>
-      </c>
-      <c r="AG67">
-        <v>260750000</v>
-      </c>
-      <c r="AH67" t="s">
-        <v>58</v>
-      </c>
-      <c r="AI67" t="s">
-        <v>49</v>
-      </c>
-      <c r="AJ67" t="s">
-        <v>393</v>
-      </c>
-      <c r="AK67" t="s">
-        <v>394</v>
-      </c>
-      <c r="AL67" s="5">
-        <f t="shared" ref="AL67:AL70" ca="1" si="3">G67-$AQ$2</f>
-        <v>395</v>
-      </c>
-      <c r="AM67" s="3">
-        <f t="shared" ref="AM67:AM70" ca="1" si="4">AL67/365</f>
-        <v>1.0821917808219179</v>
-      </c>
-      <c r="AN67" t="str">
-        <f t="shared" ref="AN67:AN70" ca="1" si="5">IF(AM67&gt;36,"&gt;36y",ROUND(AM67,0)&amp;"y")</f>
-        <v>1y</v>
-      </c>
-      <c r="AO67" t="s">
-        <v>49</v>
-      </c>
-      <c r="AP67">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.25">
-      <c r="B68" t="s">
-        <v>447</v>
-      </c>
-      <c r="C68" t="s">
-        <v>282</v>
-      </c>
-      <c r="D68" t="s">
-        <v>448</v>
-      </c>
-      <c r="E68" t="s">
-        <v>449</v>
-      </c>
-      <c r="F68" t="s">
-        <v>450</v>
-      </c>
-      <c r="G68" t="s">
-        <v>451</v>
-      </c>
-      <c r="H68" t="s">
-        <v>42</v>
-      </c>
-      <c r="I68" t="s">
-        <v>43</v>
-      </c>
-      <c r="J68">
-        <v>9.65</v>
-      </c>
-      <c r="K68" t="s">
-        <v>44</v>
-      </c>
-      <c r="L68" t="s">
-        <v>45</v>
-      </c>
-      <c r="M68">
-        <v>1</v>
-      </c>
-      <c r="N68" t="s">
-        <v>46</v>
-      </c>
-      <c r="O68" t="s">
-        <v>44</v>
-      </c>
-      <c r="P68" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q68" t="s">
-        <v>48</v>
-      </c>
-      <c r="R68" t="s">
-        <v>49</v>
-      </c>
-      <c r="S68">
-        <v>1</v>
-      </c>
-      <c r="T68">
-        <v>-105.66356298379293</v>
-      </c>
-      <c r="U68">
-        <v>12.899488999999999</v>
-      </c>
-      <c r="V68" t="s">
-        <v>49</v>
-      </c>
-      <c r="W68" t="s">
-        <v>49</v>
-      </c>
-      <c r="X68" t="s">
-        <v>287</v>
-      </c>
-      <c r="Y68" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z68" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA68" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB68" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC68" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD68" t="s">
-        <v>452</v>
-      </c>
-      <c r="AE68" t="s">
-        <v>57</v>
-      </c>
-      <c r="AF68">
-        <v>58800000</v>
-      </c>
-      <c r="AG68">
-        <v>58800000</v>
-      </c>
-      <c r="AH68" t="s">
-        <v>58</v>
-      </c>
-      <c r="AI68" t="s">
-        <v>49</v>
-      </c>
-      <c r="AJ68" t="s">
-        <v>59</v>
-      </c>
-      <c r="AK68" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL68" s="5">
-        <f t="shared" ca="1" si="3"/>
-        <v>2283</v>
-      </c>
-      <c r="AM68" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>6.2547945205479456</v>
-      </c>
-      <c r="AN68" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v>6y</v>
-      </c>
-      <c r="AO68">
-        <v>87.180999999999997</v>
-      </c>
-      <c r="AP68">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.25">
-      <c r="B69" t="s">
-        <v>453</v>
-      </c>
-      <c r="C69" t="s">
-        <v>135</v>
-      </c>
-      <c r="D69" t="s">
-        <v>454</v>
-      </c>
-      <c r="E69" t="s">
-        <v>455</v>
-      </c>
-      <c r="F69" t="s">
-        <v>456</v>
-      </c>
-      <c r="G69" t="s">
-        <v>457</v>
-      </c>
-      <c r="H69" t="s">
-        <v>42</v>
-      </c>
-      <c r="I69" t="s">
-        <v>79</v>
-      </c>
-      <c r="J69">
-        <v>0</v>
-      </c>
-      <c r="K69" t="s">
-        <v>44</v>
-      </c>
-      <c r="L69" t="s">
-        <v>45</v>
-      </c>
-      <c r="M69">
-        <v>1</v>
-      </c>
-      <c r="N69" t="s">
-        <v>46</v>
-      </c>
-      <c r="O69" t="s">
-        <v>44</v>
-      </c>
-      <c r="P69" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q69" t="s">
-        <v>48</v>
-      </c>
-      <c r="R69" t="s">
-        <v>47</v>
-      </c>
-      <c r="S69" t="s">
-        <v>44</v>
-      </c>
-      <c r="T69">
-        <v>-94.463254019144216</v>
-      </c>
-      <c r="U69">
-        <v>12.723623</v>
-      </c>
-      <c r="V69" t="s">
-        <v>49</v>
-      </c>
-      <c r="W69" t="s">
-        <v>49</v>
-      </c>
-      <c r="X69" t="s">
-        <v>140</v>
-      </c>
-      <c r="Y69" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z69" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA69" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB69" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC69" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD69" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE69" t="s">
-        <v>57</v>
-      </c>
-      <c r="AF69">
-        <v>72000000</v>
-      </c>
-      <c r="AG69">
-        <v>72000000</v>
-      </c>
-      <c r="AH69" t="s">
-        <v>58</v>
-      </c>
-      <c r="AI69" t="s">
-        <v>49</v>
-      </c>
-      <c r="AJ69" t="s">
-        <v>142</v>
-      </c>
-      <c r="AK69" t="s">
-        <v>143</v>
-      </c>
-      <c r="AL69" s="5">
-        <f t="shared" ca="1" si="3"/>
-        <v>1157</v>
-      </c>
-      <c r="AM69" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>3.1698630136986301</v>
-      </c>
-      <c r="AN69" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v>3y</v>
-      </c>
-      <c r="AO69">
-        <v>68.972999999999999</v>
-      </c>
-      <c r="AP69">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.25">
-      <c r="B70" t="s">
-        <v>458</v>
-      </c>
-      <c r="C70" t="s">
-        <v>135</v>
-      </c>
-      <c r="D70" t="s">
-        <v>459</v>
-      </c>
-      <c r="E70" t="s">
-        <v>460</v>
-      </c>
-      <c r="F70" t="s">
-        <v>461</v>
-      </c>
-      <c r="G70" t="s">
-        <v>462</v>
-      </c>
-      <c r="H70" t="s">
-        <v>42</v>
-      </c>
-      <c r="I70" t="s">
-        <v>43</v>
-      </c>
-      <c r="J70">
-        <v>9.5</v>
-      </c>
-      <c r="K70" t="s">
-        <v>44</v>
-      </c>
-      <c r="L70" t="s">
-        <v>45</v>
-      </c>
-      <c r="M70">
-        <v>1</v>
-      </c>
-      <c r="N70" t="s">
-        <v>46</v>
-      </c>
-      <c r="O70" t="s">
-        <v>44</v>
-      </c>
-      <c r="P70" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q70" t="s">
-        <v>48</v>
-      </c>
-      <c r="R70" t="s">
-        <v>47</v>
-      </c>
-      <c r="S70">
-        <v>2</v>
-      </c>
-      <c r="T70">
-        <v>-62.836857008190528</v>
-      </c>
-      <c r="U70">
-        <v>13.216260999999999</v>
-      </c>
-      <c r="V70" t="s">
-        <v>49</v>
-      </c>
-      <c r="W70" t="s">
-        <v>49</v>
-      </c>
-      <c r="X70" t="s">
-        <v>140</v>
-      </c>
-      <c r="Y70" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z70" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA70" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB70" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC70" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD70" t="s">
-        <v>463</v>
-      </c>
-      <c r="AE70" t="s">
-        <v>57</v>
-      </c>
-      <c r="AF70">
-        <v>6000000</v>
-      </c>
-      <c r="AG70">
-        <v>6000000</v>
-      </c>
-      <c r="AH70" t="s">
-        <v>58</v>
-      </c>
-      <c r="AI70" t="s">
-        <v>49</v>
-      </c>
-      <c r="AJ70" t="s">
-        <v>142</v>
-      </c>
-      <c r="AK70" t="s">
-        <v>143</v>
-      </c>
-      <c r="AL70" s="5">
-        <f t="shared" ca="1" si="3"/>
-        <v>695</v>
-      </c>
-      <c r="AM70" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>1.904109589041096</v>
-      </c>
-      <c r="AN70" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v>2y</v>
-      </c>
-      <c r="AO70">
-        <v>94.644000000000005</v>
-      </c>
-      <c r="AP70">
-        <v>1000</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="B1:AK70" xr:uid="{3E3BFF2A-B712-459A-8265-CC1EA8C41DE6}"/>
+  <autoFilter ref="B1:AQ64" xr:uid="{3E3BFF2A-B712-459A-8265-CC1EA8C41DE6}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/datos_y_modelos/Domestic/supra.xlsx
+++ b/datos_y_modelos/Domestic/supra.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{9A6F68A9-FCC5-4E77-BF6D-576ACF924730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EC0627F6-2DC6-4AF1-9A23-F0938631E874}"/>
+    <workbookView xWindow="0" yWindow="10580" windowWidth="19240" windowHeight="11620" xr2:uid="{EC0627F6-2DC6-4AF1-9A23-F0938631E874}"/>
   </bookViews>
   <sheets>
     <sheet name="db_values_only" sheetId="1" r:id="rId1"/>
@@ -3825,11 +3825,11 @@
       </c>
       <c r="AL2" s="5">
         <f ca="1">G2-$AQ$2</f>
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="AM2" s="3">
         <f ca="1">AL2/365</f>
-        <v>0.56438356164383563</v>
+        <v>0.53150684931506853</v>
       </c>
       <c r="AN2" t="str">
         <f ca="1">IF(AM2&gt;36,"&gt;36y",ROUND(AM2,0)&amp;"y")</f>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="AQ2" s="4">
         <f ca="1">TODAY()</f>
-        <v>45838</v>
+        <v>45850</v>
       </c>
     </row>
     <row r="3" spans="2:43" x14ac:dyDescent="0.25">
@@ -3957,11 +3957,11 @@
       </c>
       <c r="AL3" s="5">
         <f t="shared" ref="AL3:AL61" ca="1" si="0">G3-$AQ$2</f>
-        <v>960</v>
+        <v>948</v>
       </c>
       <c r="AM3" s="3">
         <f t="shared" ref="AM3:AM61" ca="1" si="1">AL3/365</f>
-        <v>2.6301369863013697</v>
+        <v>2.5972602739726027</v>
       </c>
       <c r="AN3" t="str">
         <f t="shared" ref="AN3:AN61" ca="1" si="2">IF(AM3&gt;36,"&gt;36y",ROUND(AM3,0)&amp;"y")</f>
@@ -4085,11 +4085,11 @@
       </c>
       <c r="AL4" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>1320</v>
+        <v>1308</v>
       </c>
       <c r="AM4" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>3.6164383561643834</v>
+        <v>3.5835616438356164</v>
       </c>
       <c r="AN4" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4213,11 +4213,11 @@
       </c>
       <c r="AL5" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>4606</v>
+        <v>4594</v>
       </c>
       <c r="AM5" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>12.61917808219178</v>
+        <v>12.586301369863014</v>
       </c>
       <c r="AN5" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4341,11 +4341,11 @@
       </c>
       <c r="AL6" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>2408</v>
+        <v>2396</v>
       </c>
       <c r="AM6" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>6.5972602739726032</v>
+        <v>6.5643835616438357</v>
       </c>
       <c r="AN6" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4469,11 +4469,11 @@
       </c>
       <c r="AL7" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="AM7" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5808219178082192</v>
+        <v>1.547945205479452</v>
       </c>
       <c r="AN7" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4597,11 +4597,11 @@
       </c>
       <c r="AL8" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>2292</v>
+        <v>2280</v>
       </c>
       <c r="AM8" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>6.279452054794521</v>
+        <v>6.2465753424657535</v>
       </c>
       <c r="AN8" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4725,11 +4725,11 @@
       </c>
       <c r="AL9" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>5719</v>
+        <v>5707</v>
       </c>
       <c r="AM9" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>15.668493150684931</v>
+        <v>15.635616438356164</v>
       </c>
       <c r="AN9" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4853,11 +4853,11 @@
       </c>
       <c r="AL10" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="AM10" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.60273972602739723</v>
+        <v>0.56986301369863013</v>
       </c>
       <c r="AN10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4981,11 +4981,11 @@
       </c>
       <c r="AL11" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="AM11" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>1.252054794520548</v>
+        <v>1.2191780821917808</v>
       </c>
       <c r="AN11" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5109,11 +5109,11 @@
       </c>
       <c r="AL12" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="AM12" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.33150684931506852</v>
+        <v>0.29863013698630136</v>
       </c>
       <c r="AN12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5237,11 +5237,11 @@
       </c>
       <c r="AL13" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>6083</v>
+        <v>6071</v>
       </c>
       <c r="AM13" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>16.665753424657535</v>
+        <v>16.632876712328766</v>
       </c>
       <c r="AN13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5365,11 +5365,11 @@
       </c>
       <c r="AL14" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>3522</v>
+        <v>3510</v>
       </c>
       <c r="AM14" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>9.6493150684931503</v>
+        <v>9.6164383561643838</v>
       </c>
       <c r="AN14" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5493,11 +5493,11 @@
       </c>
       <c r="AL15" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>928</v>
+        <v>916</v>
       </c>
       <c r="AM15" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>2.5424657534246577</v>
+        <v>2.5095890410958903</v>
       </c>
       <c r="AN15" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5621,11 +5621,11 @@
       </c>
       <c r="AL16" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>4348</v>
+        <v>4336</v>
       </c>
       <c r="AM16" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>11.912328767123288</v>
+        <v>11.87945205479452</v>
       </c>
       <c r="AN16" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5749,11 +5749,11 @@
       </c>
       <c r="AL17" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>1054</v>
+        <v>1042</v>
       </c>
       <c r="AM17" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>2.8876712328767122</v>
+        <v>2.8547945205479452</v>
       </c>
       <c r="AN17" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5877,11 +5877,11 @@
       </c>
       <c r="AL18" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>1785</v>
+        <v>1773</v>
       </c>
       <c r="AM18" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>4.8904109589041092</v>
+        <v>4.8575342465753426</v>
       </c>
       <c r="AN18" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -6005,11 +6005,11 @@
       </c>
       <c r="AL19" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>1661</v>
+        <v>1649</v>
       </c>
       <c r="AM19" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>4.5506849315068489</v>
+        <v>4.5178082191780824</v>
       </c>
       <c r="AN19" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -6133,11 +6133,11 @@
       </c>
       <c r="AL20" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>2817</v>
+        <v>2805</v>
       </c>
       <c r="AM20" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>7.7178082191780826</v>
+        <v>7.6849315068493151</v>
       </c>
       <c r="AN20" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -6261,11 +6261,11 @@
       </c>
       <c r="AL21" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>1519</v>
+        <v>1507</v>
       </c>
       <c r="AM21" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>4.161643835616438</v>
+        <v>4.1287671232876715</v>
       </c>
       <c r="AN21" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -6389,11 +6389,11 @@
       </c>
       <c r="AL22" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>1570</v>
+        <v>1558</v>
       </c>
       <c r="AM22" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>4.3013698630136989</v>
+        <v>4.2684931506849315</v>
       </c>
       <c r="AN22" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -6517,11 +6517,11 @@
       </c>
       <c r="AL23" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>4642</v>
+        <v>4630</v>
       </c>
       <c r="AM23" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>12.717808219178082</v>
+        <v>12.684931506849315</v>
       </c>
       <c r="AN23" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -6645,11 +6645,11 @@
       </c>
       <c r="AL24" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="AM24" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73972602739726023</v>
+        <v>0.70684931506849313</v>
       </c>
       <c r="AN24" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -6773,11 +6773,11 @@
       </c>
       <c r="AL25" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="AM25" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>-3.287671232876712E-2</v>
       </c>
       <c r="AN25" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -6901,11 +6901,11 @@
       </c>
       <c r="AL26" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>695</v>
+        <v>683</v>
       </c>
       <c r="AM26" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>1.904109589041096</v>
+        <v>1.8712328767123287</v>
       </c>
       <c r="AN26" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -7029,11 +7029,11 @@
       </c>
       <c r="AL27" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="AM27" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5972602739726027</v>
+        <v>1.5643835616438355</v>
       </c>
       <c r="AN27" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -7157,11 +7157,11 @@
       </c>
       <c r="AL28" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="AM28" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5616438356164384</v>
+        <v>1.5287671232876712</v>
       </c>
       <c r="AN28" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -7285,11 +7285,11 @@
       </c>
       <c r="AL29" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>4881</v>
+        <v>4869</v>
       </c>
       <c r="AM29" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>13.372602739726027</v>
+        <v>13.33972602739726</v>
       </c>
       <c r="AN29" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -7413,11 +7413,11 @@
       </c>
       <c r="AL30" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>949</v>
+        <v>937</v>
       </c>
       <c r="AM30" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>2.6</v>
+        <v>2.5671232876712327</v>
       </c>
       <c r="AN30" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -7541,11 +7541,11 @@
       </c>
       <c r="AL31" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>2827</v>
+        <v>2815</v>
       </c>
       <c r="AM31" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>7.7452054794520544</v>
+        <v>7.7123287671232879</v>
       </c>
       <c r="AN31" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -7669,11 +7669,11 @@
       </c>
       <c r="AL32" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AM32" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>4.3835616438356165E-2</v>
+        <v>1.0958904109589041E-2</v>
       </c>
       <c r="AN32" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -7797,11 +7797,11 @@
       </c>
       <c r="AL33" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>1299</v>
+        <v>1287</v>
       </c>
       <c r="AM33" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>3.558904109589041</v>
+        <v>3.526027397260274</v>
       </c>
       <c r="AN33" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -7925,11 +7925,11 @@
       </c>
       <c r="AL34" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>2234</v>
+        <v>2222</v>
       </c>
       <c r="AM34" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>6.1205479452054794</v>
+        <v>6.087671232876712</v>
       </c>
       <c r="AN34" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8053,11 +8053,11 @@
       </c>
       <c r="AL35" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>1661</v>
+        <v>1649</v>
       </c>
       <c r="AM35" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>4.5506849315068489</v>
+        <v>4.5178082191780824</v>
       </c>
       <c r="AN35" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8181,11 +8181,11 @@
       </c>
       <c r="AL36" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="AM36" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>1.2082191780821918</v>
+        <v>1.1753424657534246</v>
       </c>
       <c r="AN36" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8309,11 +8309,11 @@
       </c>
       <c r="AL37" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>861</v>
+        <v>849</v>
       </c>
       <c r="AM37" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>2.3589041095890413</v>
+        <v>2.3260273972602739</v>
       </c>
       <c r="AN37" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8437,11 +8437,11 @@
       </c>
       <c r="AL38" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>2073</v>
+        <v>2061</v>
       </c>
       <c r="AM38" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>5.6794520547945204</v>
+        <v>5.646575342465753</v>
       </c>
       <c r="AN38" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8565,15 +8565,15 @@
       </c>
       <c r="AL39" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>1653</v>
+        <v>1641</v>
       </c>
       <c r="AM39" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>4.5287671232876709</v>
+        <v>4.4958904109589044</v>
       </c>
       <c r="AN39" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>5y</v>
+        <v>4y</v>
       </c>
       <c r="AO39">
         <v>86.162000000000006</v>
@@ -8693,11 +8693,11 @@
       </c>
       <c r="AL40" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="AM40" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>1.0027397260273974</v>
+        <v>0.96986301369863015</v>
       </c>
       <c r="AN40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8821,11 +8821,11 @@
       </c>
       <c r="AL41" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="AM41" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.55890410958904113</v>
+        <v>0.52602739726027392</v>
       </c>
       <c r="AN41" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8949,11 +8949,11 @@
       </c>
       <c r="AL42" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>1455</v>
+        <v>1443</v>
       </c>
       <c r="AM42" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>3.9863013698630136</v>
+        <v>3.9534246575342467</v>
       </c>
       <c r="AN42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9077,11 +9077,11 @@
       </c>
       <c r="AL43" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>3262</v>
+        <v>3250</v>
       </c>
       <c r="AM43" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>8.9369863013698634</v>
+        <v>8.9041095890410951</v>
       </c>
       <c r="AN43" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9205,11 +9205,11 @@
       </c>
       <c r="AL44" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="AM44" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.53972602739726028</v>
+        <v>0.50684931506849318</v>
       </c>
       <c r="AN44" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9333,11 +9333,11 @@
       </c>
       <c r="AL45" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>870</v>
+        <v>858</v>
       </c>
       <c r="AM45" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>2.3835616438356166</v>
+        <v>2.3506849315068492</v>
       </c>
       <c r="AN45" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9461,11 +9461,11 @@
       </c>
       <c r="AL46" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>1848</v>
+        <v>1836</v>
       </c>
       <c r="AM46" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>5.0630136986301366</v>
+        <v>5.0301369863013701</v>
       </c>
       <c r="AN46" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9589,11 +9589,11 @@
       </c>
       <c r="AL47" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="AM47" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74794520547945209</v>
+        <v>0.71506849315068488</v>
       </c>
       <c r="AN47" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9717,11 +9717,11 @@
       </c>
       <c r="AL48" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>981</v>
+        <v>969</v>
       </c>
       <c r="AM48" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>2.6876712328767125</v>
+        <v>2.6547945205479451</v>
       </c>
       <c r="AN48" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9845,11 +9845,11 @@
       </c>
       <c r="AL49" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="AM49" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.76986301369863008</v>
+        <v>0.73698630136986298</v>
       </c>
       <c r="AN49" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9973,11 +9973,11 @@
       </c>
       <c r="AL50" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>1884</v>
+        <v>1872</v>
       </c>
       <c r="AM50" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>5.161643835616438</v>
+        <v>5.1287671232876715</v>
       </c>
       <c r="AN50" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10101,11 +10101,11 @@
       </c>
       <c r="AL51" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>2234</v>
+        <v>2222</v>
       </c>
       <c r="AM51" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>6.1205479452054794</v>
+        <v>6.087671232876712</v>
       </c>
       <c r="AN51" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10229,11 +10229,11 @@
       </c>
       <c r="AL52" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="AM52" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75342465753424659</v>
+        <v>0.72054794520547949</v>
       </c>
       <c r="AN52" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10357,11 +10357,11 @@
       </c>
       <c r="AL53" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>2205</v>
+        <v>2193</v>
       </c>
       <c r="AM53" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>6.0410958904109586</v>
+        <v>6.0082191780821921</v>
       </c>
       <c r="AN53" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10485,11 +10485,11 @@
       </c>
       <c r="AL54" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="AM54" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.34794520547945207</v>
+        <v>0.31506849315068491</v>
       </c>
       <c r="AN54" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10613,11 +10613,11 @@
       </c>
       <c r="AL55" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>2142</v>
+        <v>2130</v>
       </c>
       <c r="AM55" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>5.8684931506849312</v>
+        <v>5.8356164383561646</v>
       </c>
       <c r="AN55" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10741,11 +10741,11 @@
       </c>
       <c r="AL56" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>837</v>
+        <v>825</v>
       </c>
       <c r="AM56" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>2.2931506849315069</v>
+        <v>2.2602739726027399</v>
       </c>
       <c r="AN56" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10869,11 +10869,11 @@
       </c>
       <c r="AL57" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>3054</v>
+        <v>3042</v>
       </c>
       <c r="AM57" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>8.367123287671232</v>
+        <v>8.3342465753424655</v>
       </c>
       <c r="AN57" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10997,11 +10997,11 @@
       </c>
       <c r="AL58" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>879</v>
+        <v>867</v>
       </c>
       <c r="AM58" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>2.408219178082192</v>
+        <v>2.3753424657534246</v>
       </c>
       <c r="AN58" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11125,11 +11125,11 @@
       </c>
       <c r="AL59" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="AM59" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.23561643835616439</v>
+        <v>0.20273972602739726</v>
       </c>
       <c r="AN59" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11253,11 +11253,11 @@
       </c>
       <c r="AL60" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="AM60" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>1.021917808219178</v>
+        <v>0.989041095890411</v>
       </c>
       <c r="AN60" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11381,11 +11381,11 @@
       </c>
       <c r="AL61" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>1152</v>
+        <v>1140</v>
       </c>
       <c r="AM61" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>3.1561643835616437</v>
+        <v>3.1232876712328768</v>
       </c>
       <c r="AN61" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11509,11 +11509,11 @@
       </c>
       <c r="AL62" s="5">
         <f t="shared" ref="AL62:AL64" ca="1" si="3">G62-$AQ$2</f>
-        <v>2282</v>
+        <v>2270</v>
       </c>
       <c r="AM62" s="3">
         <f t="shared" ref="AM62:AM64" ca="1" si="4">AL62/365</f>
-        <v>6.2520547945205482</v>
+        <v>6.2191780821917808</v>
       </c>
       <c r="AN62" t="str">
         <f t="shared" ref="AN62:AN64" ca="1" si="5">IF(AM62&gt;36,"&gt;36y",ROUND(AM62,0)&amp;"y")</f>
@@ -11637,11 +11637,11 @@
       </c>
       <c r="AL63" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>1156</v>
+        <v>1144</v>
       </c>
       <c r="AM63" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>3.1671232876712327</v>
+        <v>3.1342465753424658</v>
       </c>
       <c r="AN63" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -11765,11 +11765,11 @@
       </c>
       <c r="AL64" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>694</v>
+        <v>682</v>
       </c>
       <c r="AM64" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>1.9013698630136986</v>
+        <v>1.8684931506849316</v>
       </c>
       <c r="AN64" t="str">
         <f t="shared" ca="1" si="5"/>
